--- a/Стратегия тестирования.xlsx
+++ b/Стратегия тестирования.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="6" rupBuild="9302"/>
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="-105" windowWidth="20730" windowHeight="11760" tabRatio="397" firstSheet="1" activeTab="5"/>
+    <workbookView xWindow="-105" yWindow="-105" windowWidth="20730" windowHeight="11760" tabRatio="397" firstSheet="2" activeTab="6"/>
   </bookViews>
   <sheets>
     <sheet name="Тест-план" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="422" uniqueCount="218">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="422" uniqueCount="219">
   <si>
     <t>Цели доработки</t>
   </si>
@@ -767,16 +767,27 @@
 </t>
     </r>
   </si>
+  <si>
+    <t>Кнопка регистрации неактивна</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="35" x14ac:knownFonts="1">
+  <fonts count="36" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
@@ -2073,243 +2084,231 @@
   </borders>
   <cellStyleXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="9"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="9"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="9"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="9" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="9"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="9"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="9"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="9" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="9"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="9"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="9" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="9"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="9" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="9"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="9" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="9"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="9"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="9"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="9"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="9"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="9"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="9" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="9"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="9" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="9"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="9" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="9"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="9"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="9" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="9"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="9"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="9" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="9"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="9"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="9"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="9"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="9"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="9"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="9" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="9" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="9" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9"/>
   </cellStyleXfs>
-  <cellXfs count="337">
+  <cellXfs count="338">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" xfId="5" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" xfId="5" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" xfId="5" applyFont="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" xfId="5" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" xfId="5" applyFont="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" xfId="5" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" xfId="5" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" xfId="5" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" xfId="5" applyFont="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" xfId="11"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="11" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="11" applyFont="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" xfId="5" applyFont="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="9" xfId="11"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="11" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="11" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="11" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="9" xfId="11" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="11" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" xfId="20"/>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="9" xfId="20"/>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="24" xfId="29" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="24" xfId="29" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="24" xfId="29" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="29" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="24" xfId="29" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="24" xfId="29" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="29" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="29" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="24" xfId="29" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="29" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="9" xfId="29" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="41" xfId="29" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="42" xfId="29" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="39" xfId="29" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="24" xfId="29" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="9" xfId="29" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="24" xfId="29" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="29" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="24" xfId="29" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="29" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="24" xfId="29" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="24" xfId="29" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="24" xfId="29" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="24" xfId="29" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="24" xfId="29" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="8" borderId="24" xfId="29" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -2318,652 +2317,667 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="29" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="29" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="24" xfId="29" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="24" xfId="29" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="9" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="27" fillId="9" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="9" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="28" fillId="9" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="9" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="28" fillId="9" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="9" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="28" fillId="9" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="9" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="26" fillId="9" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="27" fillId="9" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="28" fillId="9" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="9" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
+    <xf numFmtId="0" fontId="28" fillId="9" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="28" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="9" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="28" fillId="9" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="9" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="9" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="28" fillId="0" borderId="58" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="9" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="5" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="28" fillId="5" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="5" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="27" fillId="5" borderId="63" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="27" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="9" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="27" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="27" fillId="5" borderId="64" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="27" fillId="5" borderId="65" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="28" fillId="5" borderId="65" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="9" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="31" fillId="5" borderId="65" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="27" fillId="5" borderId="66" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="28" fillId="9" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="28" fillId="9" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="28" fillId="9" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="9" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="28" fillId="8" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="28" fillId="8" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="27" fillId="9" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="28" fillId="9" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="9" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="28" fillId="9" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="9" fontId="28" fillId="9" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="28" fillId="9" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="9" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
+    <xf numFmtId="0" fontId="28" fillId="9" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="28" fillId="9" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="9" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="9" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="9" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="9" borderId="59" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="14" fontId="27" fillId="0" borderId="58" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="9" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="61" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="9" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="28" fillId="9" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="28" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="9" borderId="67" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="9" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="9" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="9" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="9" borderId="68" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="5" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="27" fillId="5" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="5" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="26" fillId="5" borderId="63" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="26" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="26" fillId="5" borderId="64" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="26" fillId="5" borderId="65" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="27" fillId="5" borderId="65" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="5" borderId="65" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="26" fillId="5" borderId="66" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="27" fillId="9" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="9" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="27" fillId="9" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="9" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="9" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="9" fontId="27" fillId="9" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="27" fillId="9" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="9" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="27" fillId="9" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="9" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="27" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="24" xfId="29" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="24" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="70" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="70" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="9" borderId="71" xfId="5" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="27" fillId="9" borderId="73" xfId="5" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="57" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="9" borderId="75" xfId="5" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="76" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="41" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="41" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="9" borderId="36" xfId="5" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="27" fillId="9" borderId="54" xfId="5" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="27" fillId="9" borderId="60" xfId="5" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="5" borderId="62" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="5" borderId="62" xfId="5" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="63" xfId="5" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="9" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="5" borderId="9" xfId="5" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="64" xfId="5" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="5" borderId="65" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="5" borderId="65" xfId="5" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="66" xfId="5" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="27" fillId="5" borderId="9" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="5" borderId="65" xfId="5" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="40" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="24" xfId="29" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="8" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="2" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="6" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="6" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="20" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="24" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="2" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="22" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="25" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="4" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="26" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="24" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="12" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="24" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="24" xfId="5" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="24" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="28" fillId="0" borderId="58" xfId="5" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="28" fillId="0" borderId="57" xfId="5" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="78" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="56" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="5" borderId="9" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="5" borderId="62" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="5" borderId="62" xfId="5" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="27" fillId="5" borderId="63" xfId="5" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="27" fillId="5" borderId="65" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="5" borderId="65" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="5" borderId="65" xfId="5" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="27" fillId="5" borderId="66" xfId="5" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="24" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="24" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="24" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="24" xfId="6" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="24" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="24" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="70" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="57" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="76" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="41" xfId="11" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="28" fillId="0" borderId="58" xfId="11" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="9" borderId="36" xfId="11" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="27" fillId="9" borderId="54" xfId="11" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="27" fillId="9" borderId="60" xfId="11" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="31" fillId="5" borderId="62" xfId="11" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="27" fillId="5" borderId="63" xfId="11" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="31" fillId="5" borderId="9" xfId="11" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="27" fillId="5" borderId="64" xfId="11" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="27" fillId="5" borderId="65" xfId="11" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="28" fillId="5" borderId="65" xfId="11" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="5" borderId="65" xfId="11" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="27" fillId="5" borderId="66" xfId="11" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="28" fillId="9" borderId="13" xfId="11" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="9" borderId="14" xfId="11" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="28" fillId="9" borderId="15" xfId="11" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="9" borderId="15" xfId="11" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="9" borderId="16" xfId="11" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="9" fontId="28" fillId="9" borderId="17" xfId="11" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="28" fillId="9" borderId="18" xfId="11" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="9" borderId="15" xfId="11" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="28" fillId="9" borderId="16" xfId="11" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="28" fillId="9" borderId="17" xfId="11" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="2" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="6" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="20" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="2" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="22" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="4" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="4" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="26" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="24" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="24" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="6" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="2" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="25" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="4" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="24" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="19" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="21" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="43" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="24" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="9" borderId="24" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="9" borderId="77" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="9" borderId="14" xfId="5" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="28" fillId="9" borderId="15" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="9" borderId="15" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="9" borderId="16" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="9" fontId="28" fillId="9" borderId="17" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="28" fillId="9" borderId="33" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="9" borderId="15" xfId="5" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="28" fillId="9" borderId="16" xfId="5" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="28" fillId="9" borderId="17" xfId="5" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="28" fillId="9" borderId="13" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="9" borderId="44" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="9" borderId="45" xfId="5" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="28" fillId="9" borderId="45" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="9" borderId="46" xfId="5" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="28" fillId="9" borderId="10" xfId="5" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="41" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="33" fillId="8" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="8" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="8" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="8" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="24" xfId="29" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="41" xfId="29" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="42" xfId="29" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="39" xfId="29" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="9" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="9" borderId="67" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="9" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="9" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="9" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="9" borderId="68" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="9" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="8" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="28" fillId="9" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="24" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="29" fillId="8" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="24" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="24" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="61" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="9" borderId="41" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="28" fillId="9" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="9" borderId="42" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="28" fillId="9" borderId="59" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="9" borderId="39" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="28" fillId="9" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="9" borderId="24" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="28" fillId="9" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="9" borderId="69" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="28" fillId="9" borderId="69" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="9" borderId="70" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="28" fillId="9" borderId="70" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="70" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="28" fillId="9" borderId="74" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="9" borderId="57" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="9" borderId="72" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="9" borderId="24" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="9" borderId="24" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="24" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="70" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="24" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="9" borderId="71" xfId="5" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="27" fillId="9" borderId="72" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
+    <xf numFmtId="0" fontId="28" fillId="9" borderId="69" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="9" borderId="73" xfId="5" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="27" fillId="9" borderId="74" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="28" fillId="9" borderId="70" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="9" borderId="72" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="9" borderId="24" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="9" borderId="74" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="9" borderId="57" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="9" borderId="58" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="9" borderId="57" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="28" fillId="9" borderId="59" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="57" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
+    <xf numFmtId="0" fontId="28" fillId="9" borderId="56" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="9" borderId="75" xfId="5" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="76" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="28" fillId="9" borderId="35" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="41" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="28" fillId="9" borderId="67" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="41" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="28" fillId="9" borderId="38" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="9" borderId="36" xfId="5" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="26" fillId="9" borderId="54" xfId="5" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="26" fillId="9" borderId="60" xfId="5" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="18" fillId="5" borderId="62" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="28" fillId="9" borderId="68" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="39" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="39" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="28" fillId="9" borderId="76" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="9" borderId="79" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="9" borderId="78" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="9" borderId="41" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="9" borderId="42" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="9" borderId="39" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="9" borderId="41" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="9" borderId="42" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="9" borderId="39" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="9" borderId="35" xfId="11" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="9" borderId="62" xfId="11" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="9" borderId="37" xfId="11" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="9" borderId="9" xfId="11" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="9" borderId="38" xfId="11" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="9" borderId="65" xfId="11" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="9" borderId="74" xfId="11" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="62" xfId="5" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="63" xfId="5" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="9" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="9" xfId="5" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="64" xfId="5" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="18" fillId="5" borderId="65" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="28" fillId="9" borderId="57" xfId="11" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="65" xfId="5" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="66" xfId="5" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="27" fillId="9" borderId="69" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="9" borderId="70" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="9" borderId="72" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="9" borderId="24" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="5" borderId="9" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="9" borderId="74" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="9" borderId="57" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="5" borderId="65" xfId="5" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="40" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="8" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="2" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="6" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="6" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="20" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="24" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="2" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="22" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="25" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="4" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="26" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="24" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="12" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="24" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="24" xfId="5" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="24" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="9" borderId="41" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="9" borderId="42" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="9" borderId="39" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="27" fillId="0" borderId="58" xfId="5" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="9" borderId="76" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="28" fillId="9" borderId="70" xfId="11" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="9" borderId="79" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="28" fillId="9" borderId="24" xfId="11" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="9" borderId="78" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="28" fillId="9" borderId="57" xfId="11" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="9" borderId="58" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="9" borderId="59" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="9" borderId="56" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="14" fontId="27" fillId="0" borderId="57" xfId="5" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="78" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="39" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="39" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="56" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="5" borderId="9" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="5" borderId="62" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="5" borderId="62" xfId="5" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="26" fillId="5" borderId="63" xfId="5" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="26" fillId="5" borderId="65" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="5" borderId="65" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="5" borderId="65" xfId="5" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="26" fillId="5" borderId="66" xfId="5" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="27" fillId="9" borderId="35" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="9" borderId="67" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="9" borderId="38" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="9" borderId="68" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="24" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="24" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="24" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="24" xfId="6" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="24" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="24" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="9" borderId="24" xfId="11" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="9" borderId="24" xfId="11" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="24" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="9" borderId="69" xfId="11" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="9" borderId="70" xfId="11" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="70" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="9" borderId="70" xfId="11" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="9" borderId="72" xfId="11" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="9" borderId="74" xfId="11" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="9" borderId="57" xfId="11" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="57" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="9" borderId="57" xfId="11" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="76" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="41" xfId="11" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="27" fillId="0" borderId="58" xfId="11" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="9" borderId="36" xfId="11" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="26" fillId="9" borderId="54" xfId="11" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="26" fillId="9" borderId="60" xfId="11" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="27" fillId="9" borderId="9" xfId="11" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="9" borderId="35" xfId="11" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="9" borderId="62" xfId="11" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="5" borderId="62" xfId="11" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="26" fillId="5" borderId="63" xfId="11" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="27" fillId="9" borderId="37" xfId="11" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="5" borderId="9" xfId="11" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="26" fillId="5" borderId="64" xfId="11" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="27" fillId="9" borderId="38" xfId="11" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="9" borderId="65" xfId="11" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="5" borderId="65" xfId="11" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="27" fillId="5" borderId="65" xfId="11" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="5" borderId="65" xfId="11" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="26" fillId="5" borderId="66" xfId="11" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="27" fillId="9" borderId="13" xfId="11" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="9" borderId="14" xfId="11" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="27" fillId="9" borderId="15" xfId="11" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="9" borderId="15" xfId="11" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="9" borderId="16" xfId="11" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="9" fontId="27" fillId="9" borderId="17" xfId="11" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="27" fillId="9" borderId="18" xfId="11" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="9" borderId="15" xfId="11" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="27" fillId="9" borderId="16" xfId="11" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="27" fillId="9" borderId="17" xfId="11" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="2" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="6" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="20" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="2" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="22" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="4" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="4" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="26" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="24" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="0" borderId="24" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="6" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="2" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="25" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="4" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="24" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="19" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="21" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="43" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="24" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="9" borderId="77" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="28" fillId="9" borderId="69" xfId="11" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="9" borderId="14" xfId="5" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="27" fillId="9" borderId="15" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="9" borderId="15" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="28" fillId="9" borderId="70" xfId="11" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="9" borderId="16" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
+    <xf numFmtId="0" fontId="28" fillId="9" borderId="72" xfId="11" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="9" fontId="27" fillId="9" borderId="17" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="27" fillId="9" borderId="33" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="28" fillId="9" borderId="24" xfId="11" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="9" borderId="15" xfId="5" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="27" fillId="9" borderId="16" xfId="5" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="27" fillId="9" borderId="17" xfId="5" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="27" fillId="9" borderId="13" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="9" borderId="44" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="9" borderId="45" xfId="5" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="27" fillId="9" borderId="45" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="9" borderId="46" xfId="5" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="27" fillId="9" borderId="10" xfId="5" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="41" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="24" xfId="29" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="32" fillId="8" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="8" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="8" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="8" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="30">
@@ -3297,7 +3311,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -3697,7 +3711,7 @@
       <c r="Z11" s="15"/>
       <c r="AA11" s="15"/>
     </row>
-    <row r="12" spans="1:28" ht="45" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:28" ht="30" x14ac:dyDescent="0.25">
       <c r="A12" s="32" t="s">
         <v>67</v>
       </c>
@@ -33511,54 +33525,54 @@
     <col min="2" max="2" width="34.28515625" style="62" customWidth="1"/>
     <col min="3" max="3" width="35.7109375" style="62" customWidth="1"/>
     <col min="4" max="4" width="36.28515625" style="62" customWidth="1"/>
-    <col min="5" max="5" width="25.140625" style="75" customWidth="1"/>
+    <col min="5" max="5" width="25.140625" style="71" customWidth="1"/>
     <col min="6" max="6" width="6.42578125" style="62" customWidth="1"/>
-    <col min="7" max="7" width="22.7109375" style="75" customWidth="1"/>
-    <col min="8" max="8" width="21" style="75" customWidth="1"/>
-    <col min="9" max="9" width="27.42578125" style="75" customWidth="1"/>
+    <col min="7" max="7" width="22.7109375" style="71" customWidth="1"/>
+    <col min="8" max="8" width="21" style="71" customWidth="1"/>
+    <col min="9" max="9" width="27.42578125" style="71" customWidth="1"/>
     <col min="10" max="10" width="10.7109375" customWidth="1"/>
     <col min="11" max="11" width="10.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="64" t="s">
+      <c r="A1" s="263" t="s">
         <v>90</v>
       </c>
-      <c r="B1" s="65"/>
-      <c r="C1" s="65"/>
-      <c r="D1" s="65"/>
-      <c r="E1" s="66"/>
+      <c r="B1" s="264"/>
+      <c r="C1" s="264"/>
+      <c r="D1" s="264"/>
+      <c r="E1" s="265"/>
       <c r="F1" s="60"/>
-      <c r="G1" s="67" t="s">
+      <c r="G1" s="262" t="s">
         <v>92</v>
       </c>
-      <c r="H1" s="67"/>
-      <c r="I1" s="67"/>
+      <c r="H1" s="262"/>
+      <c r="I1" s="262"/>
     </row>
     <row r="2" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="77" t="s">
+      <c r="A2" s="73" t="s">
         <v>93</v>
       </c>
-      <c r="B2" s="77" t="s">
+      <c r="B2" s="73" t="s">
         <v>94</v>
       </c>
-      <c r="C2" s="77" t="s">
+      <c r="C2" s="73" t="s">
         <v>95</v>
       </c>
-      <c r="D2" s="77" t="s">
+      <c r="D2" s="73" t="s">
         <v>96</v>
       </c>
-      <c r="E2" s="77" t="s">
+      <c r="E2" s="73" t="s">
         <v>91</v>
       </c>
       <c r="F2" s="63"/>
-      <c r="G2" s="77" t="s">
+      <c r="G2" s="73" t="s">
         <v>97</v>
       </c>
-      <c r="H2" s="77" t="s">
+      <c r="H2" s="73" t="s">
         <v>98</v>
       </c>
-      <c r="I2" s="77" t="s">
+      <c r="I2" s="73" t="s">
         <v>31</v>
       </c>
     </row>
@@ -33572,10 +33586,10 @@
       <c r="C3" s="61" t="s">
         <v>103</v>
       </c>
-      <c r="D3" s="69" t="s">
+      <c r="D3" s="65" t="s">
         <v>103</v>
       </c>
-      <c r="E3" s="74"/>
+      <c r="E3" s="70"/>
       <c r="F3" s="60"/>
       <c r="G3" s="58"/>
       <c r="H3" s="58"/>
@@ -33594,7 +33608,7 @@
       <c r="D4" s="61" t="s">
         <v>150</v>
       </c>
-      <c r="E4" s="74"/>
+      <c r="E4" s="70"/>
       <c r="F4" s="60"/>
       <c r="G4" s="58"/>
       <c r="H4" s="58"/>
@@ -33607,13 +33621,13 @@
       <c r="B5" s="58" t="s">
         <v>107</v>
       </c>
-      <c r="C5" s="61" t="s">
-        <v>153</v>
-      </c>
-      <c r="D5" s="61" t="s">
-        <v>153</v>
-      </c>
-      <c r="E5" s="74"/>
+      <c r="C5" s="337" t="s">
+        <v>218</v>
+      </c>
+      <c r="D5" s="337" t="s">
+        <v>218</v>
+      </c>
+      <c r="E5" s="70"/>
       <c r="F5" s="60"/>
       <c r="G5" s="58"/>
       <c r="H5" s="58"/>
@@ -33632,7 +33646,7 @@
       <c r="D6" s="61" t="s">
         <v>158</v>
       </c>
-      <c r="E6" s="76">
+      <c r="E6" s="72">
         <v>1</v>
       </c>
       <c r="F6" s="60"/>
@@ -33642,7 +33656,7 @@
       <c r="H6" s="58" t="s">
         <v>210</v>
       </c>
-      <c r="I6" s="82" t="s">
+      <c r="I6" s="78" t="s">
         <v>101</v>
       </c>
     </row>
@@ -33653,13 +33667,13 @@
       <c r="B7" s="58" t="s">
         <v>110</v>
       </c>
-      <c r="C7" s="61" t="s">
-        <v>153</v>
-      </c>
-      <c r="D7" s="61" t="s">
-        <v>153</v>
-      </c>
-      <c r="E7" s="74"/>
+      <c r="C7" s="337" t="s">
+        <v>218</v>
+      </c>
+      <c r="D7" s="337" t="s">
+        <v>218</v>
+      </c>
+      <c r="E7" s="70"/>
       <c r="F7" s="60"/>
       <c r="G7" s="58"/>
       <c r="H7" s="58"/>
@@ -33678,7 +33692,7 @@
       <c r="D8" s="61" t="s">
         <v>131</v>
       </c>
-      <c r="E8" s="74"/>
+      <c r="E8" s="70"/>
       <c r="F8" s="60"/>
       <c r="G8" s="58"/>
       <c r="H8" s="58"/>
@@ -33697,7 +33711,7 @@
       <c r="D9" s="61" t="s">
         <v>132</v>
       </c>
-      <c r="E9" s="74"/>
+      <c r="E9" s="70"/>
       <c r="F9" s="60"/>
       <c r="G9" s="58"/>
       <c r="H9" s="58"/>
@@ -33716,7 +33730,7 @@
       <c r="D10" s="61" t="s">
         <v>133</v>
       </c>
-      <c r="E10" s="74"/>
+      <c r="E10" s="70"/>
       <c r="F10" s="60"/>
       <c r="G10" s="58"/>
       <c r="H10" s="58"/>
@@ -33735,7 +33749,7 @@
       <c r="D11" s="61" t="s">
         <v>134</v>
       </c>
-      <c r="E11" s="74"/>
+      <c r="E11" s="70"/>
       <c r="F11" s="60"/>
       <c r="G11" s="58"/>
       <c r="H11" s="58"/>
@@ -33754,7 +33768,7 @@
       <c r="D12" s="61" t="s">
         <v>135</v>
       </c>
-      <c r="E12" s="74"/>
+      <c r="E12" s="70"/>
       <c r="F12" s="60"/>
       <c r="G12" s="58"/>
       <c r="H12" s="58"/>
@@ -33773,7 +33787,7 @@
       <c r="D13" s="61" t="s">
         <v>136</v>
       </c>
-      <c r="E13" s="74"/>
+      <c r="E13" s="70"/>
       <c r="F13" s="60"/>
       <c r="G13" s="58"/>
       <c r="H13" s="58"/>
@@ -33792,7 +33806,7 @@
       <c r="D14" s="61" t="s">
         <v>137</v>
       </c>
-      <c r="E14" s="74"/>
+      <c r="E14" s="70"/>
       <c r="F14" s="60"/>
       <c r="G14" s="58"/>
       <c r="H14" s="58"/>
@@ -33811,7 +33825,7 @@
       <c r="D15" s="61" t="s">
         <v>138</v>
       </c>
-      <c r="E15" s="74"/>
+      <c r="E15" s="70"/>
       <c r="F15" s="60"/>
       <c r="G15" s="58"/>
       <c r="H15" s="58"/>
@@ -33840,7 +33854,7 @@
       <c r="H16" s="58" t="s">
         <v>214</v>
       </c>
-      <c r="I16" s="82" t="s">
+      <c r="I16" s="78" t="s">
         <v>101</v>
       </c>
     </row>
@@ -33857,7 +33871,7 @@
       <c r="D17" s="61" t="s">
         <v>140</v>
       </c>
-      <c r="E17" s="74"/>
+      <c r="E17" s="70"/>
       <c r="F17" s="60"/>
       <c r="G17" s="58"/>
       <c r="H17" s="58"/>
@@ -33873,7 +33887,7 @@
       <c r="C18" s="61" t="s">
         <v>141</v>
       </c>
-      <c r="D18" s="73" t="s">
+      <c r="D18" s="69" t="s">
         <v>207</v>
       </c>
       <c r="E18" s="57">
@@ -33903,7 +33917,7 @@
       <c r="D19" s="61" t="s">
         <v>205</v>
       </c>
-      <c r="E19" s="74"/>
+      <c r="E19" s="70"/>
       <c r="F19"/>
       <c r="G19" s="41"/>
       <c r="H19" s="41"/>
@@ -33914,22 +33928,22 @@
       <c r="B20"/>
       <c r="C20"/>
       <c r="D20"/>
-      <c r="E20" s="68"/>
+      <c r="E20" s="64"/>
       <c r="F20"/>
-      <c r="G20" s="78"/>
-      <c r="H20" s="78"/>
-      <c r="I20" s="78"/>
+      <c r="G20" s="74"/>
+      <c r="H20" s="74"/>
+      <c r="I20" s="74"/>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" s="60"/>
       <c r="B21"/>
       <c r="C21"/>
       <c r="D21"/>
-      <c r="E21" s="68"/>
+      <c r="E21" s="64"/>
       <c r="F21"/>
-      <c r="G21" s="79"/>
-      <c r="H21" s="79"/>
-      <c r="I21" s="79"/>
+      <c r="G21" s="75"/>
+      <c r="H21" s="75"/>
+      <c r="I21" s="75"/>
       <c r="J21" s="14"/>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.25">
@@ -33937,11 +33951,11 @@
       <c r="B22"/>
       <c r="C22"/>
       <c r="D22"/>
-      <c r="E22" s="68"/>
+      <c r="E22" s="64"/>
       <c r="F22" s="60"/>
-      <c r="G22" s="80"/>
-      <c r="H22" s="80"/>
-      <c r="I22" s="80"/>
+      <c r="G22" s="76"/>
+      <c r="H22" s="76"/>
+      <c r="I22" s="76"/>
       <c r="J22" s="14"/>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.25">
@@ -33949,10 +33963,10 @@
       <c r="B23"/>
       <c r="C23"/>
       <c r="D23"/>
-      <c r="E23" s="68"/>
-      <c r="G23" s="81"/>
-      <c r="H23" s="81"/>
-      <c r="I23" s="81"/>
+      <c r="E23" s="64"/>
+      <c r="G23" s="77"/>
+      <c r="H23" s="77"/>
+      <c r="I23" s="77"/>
       <c r="J23" s="14"/>
     </row>
     <row r="31" spans="1:10" ht="67.150000000000006" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -33972,154 +33986,154 @@
   <dimension ref="A1:G26"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="18.28515625" style="332" customWidth="1"/>
-    <col min="3" max="3" width="15.28515625" style="332" customWidth="1"/>
-    <col min="4" max="4" width="28.5703125" style="332" customWidth="1"/>
+    <col min="1" max="2" width="18.28515625" style="257" customWidth="1"/>
+    <col min="3" max="3" width="15.28515625" style="257" customWidth="1"/>
+    <col min="4" max="4" width="28.5703125" style="257" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="28.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="333" t="s">
+      <c r="A1" s="258" t="s">
         <v>40</v>
       </c>
-      <c r="B1" s="327" t="s">
+      <c r="B1" s="266" t="s">
         <v>214</v>
       </c>
-      <c r="C1" s="328"/>
-      <c r="D1" s="329"/>
+      <c r="C1" s="267"/>
+      <c r="D1" s="268"/>
     </row>
     <row r="2" spans="1:4" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="334" t="s">
+      <c r="A2" s="259" t="s">
         <v>26</v>
       </c>
-      <c r="B2" s="330">
+      <c r="B2" s="255">
         <v>2</v>
       </c>
-      <c r="C2" s="335" t="s">
+      <c r="C2" s="260" t="s">
         <v>41</v>
       </c>
-      <c r="D2" s="331">
+      <c r="D2" s="256">
         <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="334" t="s">
+      <c r="A3" s="259" t="s">
         <v>42</v>
       </c>
-      <c r="B3" s="331" t="s">
+      <c r="B3" s="256" t="s">
         <v>215</v>
       </c>
-      <c r="C3" s="335" t="s">
+      <c r="C3" s="260" t="s">
         <v>43</v>
       </c>
-      <c r="D3" s="323"/>
+      <c r="D3" s="254"/>
     </row>
     <row r="4" spans="1:4" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="334" t="s">
+      <c r="A4" s="259" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="323" t="s">
+      <c r="B4" s="254" t="s">
         <v>62</v>
       </c>
-      <c r="C4" s="335" t="s">
+      <c r="C4" s="260" t="s">
         <v>44</v>
       </c>
-      <c r="D4" s="323" t="s">
+      <c r="D4" s="254" t="s">
         <v>216</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="334" t="s">
+      <c r="A5" s="259" t="s">
         <v>45</v>
       </c>
-      <c r="B5" s="323" t="s">
+      <c r="B5" s="254" t="s">
         <v>55</v>
       </c>
-      <c r="C5" s="335" t="s">
+      <c r="C5" s="260" t="s">
         <v>47</v>
       </c>
-      <c r="D5" s="323" t="s">
+      <c r="D5" s="254" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="321" t="s">
+      <c r="A6" s="252" t="s">
         <v>49</v>
       </c>
-      <c r="B6" s="322" t="s">
+      <c r="B6" s="253" t="s">
         <v>37</v>
       </c>
-      <c r="C6" s="323" t="s">
+      <c r="C6" s="254" t="s">
         <v>50</v>
       </c>
-      <c r="D6" s="323"/>
+      <c r="D6" s="254"/>
     </row>
     <row r="7" spans="1:4" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="321" t="s">
+      <c r="A7" s="252" t="s">
         <v>46</v>
       </c>
-      <c r="B7" s="322" t="s">
+      <c r="B7" s="253" t="s">
         <v>48</v>
       </c>
-      <c r="C7" s="323" t="s">
+      <c r="C7" s="254" t="s">
         <v>51</v>
       </c>
-      <c r="D7" s="323"/>
+      <c r="D7" s="254"/>
     </row>
     <row r="8" spans="1:4" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="321" t="s">
+      <c r="A8" s="252" t="s">
         <v>52</v>
       </c>
-      <c r="B8" s="322" t="s">
+      <c r="B8" s="253" t="s">
         <v>53</v>
       </c>
-      <c r="C8" s="323" t="s">
+      <c r="C8" s="254" t="s">
         <v>54</v>
       </c>
-      <c r="D8" s="323"/>
+      <c r="D8" s="254"/>
     </row>
     <row r="9" spans="1:4" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="321" t="s">
+      <c r="A9" s="252" t="s">
         <v>55</v>
       </c>
-      <c r="B9" s="323"/>
-      <c r="C9" s="323" t="s">
+      <c r="B9" s="254"/>
+      <c r="C9" s="254" t="s">
         <v>56</v>
       </c>
-      <c r="D9" s="323"/>
+      <c r="D9" s="254"/>
     </row>
     <row r="10" spans="1:4" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="321" t="s">
+      <c r="A10" s="252" t="s">
         <v>57</v>
       </c>
-      <c r="B10" s="323"/>
-      <c r="C10" s="323" t="s">
+      <c r="B10" s="254"/>
+      <c r="C10" s="254" t="s">
         <v>58</v>
       </c>
-      <c r="D10" s="323"/>
+      <c r="D10" s="254"/>
     </row>
     <row r="11" spans="1:4" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="334" t="s">
+      <c r="A11" s="259" t="s">
         <v>59</v>
       </c>
-      <c r="B11" s="323" t="s">
+      <c r="B11" s="254" t="s">
         <v>88</v>
       </c>
-      <c r="C11" s="335" t="s">
+      <c r="C11" s="260" t="s">
         <v>60</v>
       </c>
-      <c r="D11" s="323" t="s">
+      <c r="D11" s="254" t="s">
         <v>85</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="277.14999999999998" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="336" t="s">
+      <c r="A12" s="261" t="s">
         <v>61</v>
       </c>
-      <c r="B12" s="324" t="s">
+      <c r="B12" s="269" t="s">
         <v>217</v>
       </c>
-      <c r="C12" s="325"/>
-      <c r="D12" s="326"/>
+      <c r="C12" s="270"/>
+      <c r="D12" s="271"/>
     </row>
     <row r="18" spans="6:7" x14ac:dyDescent="0.25">
       <c r="F18" s="26"/>
@@ -34181,72 +34195,72 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="83"/>
-      <c r="B1" s="84" t="s">
+      <c r="A1" s="79"/>
+      <c r="B1" s="80" t="s">
         <v>8</v>
       </c>
-      <c r="C1" s="85" t="s">
+      <c r="C1" s="81" t="s">
         <v>34</v>
       </c>
-      <c r="D1" s="86"/>
-      <c r="E1" s="87"/>
-      <c r="F1" s="84" t="s">
+      <c r="D1" s="82"/>
+      <c r="E1" s="83"/>
+      <c r="F1" s="80" t="s">
         <v>9</v>
       </c>
-      <c r="G1" s="88">
+      <c r="G1" s="84">
         <v>1</v>
       </c>
-      <c r="H1" s="89"/>
+      <c r="H1" s="85"/>
     </row>
     <row r="2" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A2" s="90"/>
-      <c r="B2" s="91" t="s">
+      <c r="A2" s="278"/>
+      <c r="B2" s="280" t="s">
         <v>10</v>
       </c>
-      <c r="C2" s="92" t="s">
+      <c r="C2" s="282" t="s">
         <v>89</v>
       </c>
-      <c r="D2" s="93"/>
-      <c r="E2" s="94"/>
-      <c r="F2" s="95" t="s">
+      <c r="D2" s="86"/>
+      <c r="E2" s="87"/>
+      <c r="F2" s="88" t="s">
         <v>11</v>
       </c>
-      <c r="G2" s="96" t="s">
+      <c r="G2" s="89" t="s">
         <v>35</v>
       </c>
-      <c r="H2" s="97"/>
+      <c r="H2" s="90"/>
     </row>
     <row r="3" spans="1:8" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="98"/>
-      <c r="B3" s="99"/>
-      <c r="C3" s="110"/>
-      <c r="D3" s="100"/>
-      <c r="E3" s="101"/>
-      <c r="F3" s="102" t="s">
+      <c r="A3" s="279"/>
+      <c r="B3" s="281"/>
+      <c r="C3" s="283"/>
+      <c r="D3" s="91"/>
+      <c r="E3" s="92"/>
+      <c r="F3" s="93" t="s">
         <v>12</v>
       </c>
-      <c r="G3" s="103">
+      <c r="G3" s="94">
         <v>1</v>
       </c>
-      <c r="H3" s="97"/>
+      <c r="H3" s="90"/>
     </row>
     <row r="4" spans="1:8" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="104" t="s">
+      <c r="A4" s="287" t="s">
         <v>13</v>
       </c>
-      <c r="B4" s="105"/>
-      <c r="C4" s="111" t="s">
+      <c r="B4" s="286"/>
+      <c r="C4" s="97" t="s">
         <v>87</v>
       </c>
-      <c r="D4" s="106" t="s">
+      <c r="D4" s="284" t="s">
         <v>14</v>
       </c>
-      <c r="E4" s="107"/>
-      <c r="F4" s="105"/>
-      <c r="G4" s="108">
+      <c r="E4" s="285"/>
+      <c r="F4" s="286"/>
+      <c r="G4" s="95">
         <v>45795</v>
       </c>
-      <c r="H4" s="109"/>
+      <c r="H4" s="96"/>
     </row>
     <row r="5" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="8"/>
@@ -34259,42 +34273,42 @@
       <c r="H5" s="9"/>
     </row>
     <row r="6" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A6" s="112" t="s">
+      <c r="A6" s="272" t="s">
         <v>15</v>
       </c>
-      <c r="B6" s="113"/>
-      <c r="C6" s="118" t="s">
+      <c r="B6" s="273"/>
+      <c r="C6" s="98" t="s">
         <v>143</v>
       </c>
-      <c r="D6" s="119"/>
-      <c r="E6" s="120"/>
-      <c r="F6" s="120"/>
-      <c r="G6" s="120"/>
-      <c r="H6" s="121"/>
+      <c r="D6" s="99"/>
+      <c r="E6" s="100"/>
+      <c r="F6" s="100"/>
+      <c r="G6" s="100"/>
+      <c r="H6" s="101"/>
     </row>
     <row r="7" spans="1:8" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A7" s="114"/>
-      <c r="B7" s="115"/>
-      <c r="C7" s="122" t="s">
+      <c r="A7" s="274"/>
+      <c r="B7" s="275"/>
+      <c r="C7" s="102" t="s">
         <v>163</v>
       </c>
-      <c r="D7" s="123"/>
-      <c r="E7" s="124"/>
-      <c r="F7" s="124"/>
-      <c r="G7" s="124"/>
-      <c r="H7" s="125"/>
+      <c r="D7" s="103"/>
+      <c r="E7" s="104"/>
+      <c r="F7" s="104"/>
+      <c r="G7" s="104"/>
+      <c r="H7" s="105"/>
     </row>
     <row r="8" spans="1:8" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="116"/>
-      <c r="B8" s="117"/>
-      <c r="C8" s="126" t="s">
+      <c r="A8" s="276"/>
+      <c r="B8" s="277"/>
+      <c r="C8" s="106" t="s">
         <v>212</v>
       </c>
-      <c r="D8" s="127"/>
-      <c r="E8" s="128"/>
-      <c r="F8" s="128"/>
-      <c r="G8" s="128"/>
-      <c r="H8" s="129"/>
+      <c r="D8" s="107"/>
+      <c r="E8" s="108"/>
+      <c r="F8" s="108"/>
+      <c r="G8" s="108"/>
+      <c r="H8" s="109"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="8"/>
@@ -34314,409 +34328,409 @@
       <c r="H10" s="9"/>
     </row>
     <row r="11" spans="1:8" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="130">
+      <c r="A11" s="110">
         <f>COUNTA(A13:A29)</f>
         <v>17</v>
       </c>
-      <c r="B11" s="131" t="s">
+      <c r="B11" s="111" t="s">
         <v>16</v>
       </c>
-      <c r="C11" s="132" t="s">
+      <c r="C11" s="112" t="s">
         <v>17</v>
       </c>
-      <c r="D11" s="133">
+      <c r="D11" s="113">
         <v>16</v>
       </c>
-      <c r="E11" s="133">
+      <c r="E11" s="113">
         <v>1</v>
       </c>
-      <c r="F11" s="133">
-        <f t="shared" ref="D11:F11" si="0">COUNTIF(F13:F28,"x")</f>
+      <c r="F11" s="113">
+        <f t="shared" ref="F11" si="0">COUNTIF(F13:F28,"x")</f>
         <v>0</v>
       </c>
-      <c r="G11" s="134" t="s">
+      <c r="G11" s="114" t="s">
         <v>18</v>
       </c>
-      <c r="H11" s="135">
+      <c r="H11" s="115">
         <f>(D11+E11+F11)/A11</f>
         <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A12" s="136" t="s">
+      <c r="A12" s="116" t="s">
         <v>19</v>
       </c>
-      <c r="B12" s="137" t="s">
+      <c r="B12" s="117" t="s">
         <v>20</v>
       </c>
-      <c r="C12" s="137" t="s">
+      <c r="C12" s="117" t="s">
         <v>21</v>
       </c>
-      <c r="D12" s="138" t="s">
+      <c r="D12" s="118" t="s">
         <v>22</v>
       </c>
-      <c r="E12" s="138" t="s">
+      <c r="E12" s="118" t="s">
         <v>23</v>
       </c>
-      <c r="F12" s="138" t="s">
+      <c r="F12" s="118" t="s">
         <v>24</v>
       </c>
-      <c r="G12" s="139" t="s">
+      <c r="G12" s="119" t="s">
         <v>25</v>
       </c>
-      <c r="H12" s="140" t="s">
+      <c r="H12" s="120" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="47.25" x14ac:dyDescent="0.25">
-      <c r="A13" s="141">
+      <c r="A13" s="121">
         <v>1</v>
       </c>
-      <c r="B13" s="142" t="s">
+      <c r="B13" s="122" t="s">
         <v>30</v>
       </c>
-      <c r="C13" s="142" t="s">
+      <c r="C13" s="122" t="s">
         <v>28</v>
       </c>
-      <c r="D13" s="301" t="s">
+      <c r="D13" s="232" t="s">
         <v>27</v>
       </c>
-      <c r="E13" s="301"/>
-      <c r="F13" s="143"/>
-      <c r="G13" s="142" t="s">
+      <c r="E13" s="232"/>
+      <c r="F13" s="123"/>
+      <c r="G13" s="122" t="s">
         <v>28</v>
       </c>
-      <c r="H13" s="144"/>
+      <c r="H13" s="124"/>
     </row>
     <row r="14" spans="1:8" ht="94.5" x14ac:dyDescent="0.25">
-      <c r="A14" s="141">
+      <c r="A14" s="121">
         <f t="shared" ref="A14:A25" si="1">A13 + 1</f>
         <v>2</v>
       </c>
-      <c r="B14" s="142" t="s">
+      <c r="B14" s="122" t="s">
         <v>145</v>
       </c>
-      <c r="C14" s="142" t="s">
+      <c r="C14" s="122" t="s">
         <v>29</v>
       </c>
-      <c r="D14" s="301" t="s">
+      <c r="D14" s="232" t="s">
         <v>27</v>
       </c>
-      <c r="E14" s="301"/>
-      <c r="F14" s="143"/>
-      <c r="G14" s="142" t="s">
+      <c r="E14" s="232"/>
+      <c r="F14" s="123"/>
+      <c r="G14" s="122" t="s">
         <v>29</v>
       </c>
-      <c r="H14" s="144"/>
+      <c r="H14" s="124"/>
     </row>
     <row r="15" spans="1:8" ht="63" x14ac:dyDescent="0.25">
-      <c r="A15" s="141">
+      <c r="A15" s="121">
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="B15" s="142" t="s">
+      <c r="B15" s="122" t="s">
         <v>146</v>
       </c>
-      <c r="C15" s="142" t="s">
+      <c r="C15" s="122" t="s">
         <v>147</v>
       </c>
-      <c r="D15" s="301" t="s">
+      <c r="D15" s="232" t="s">
         <v>27</v>
       </c>
-      <c r="E15" s="301"/>
-      <c r="F15" s="143"/>
-      <c r="G15" s="142" t="s">
+      <c r="E15" s="232"/>
+      <c r="F15" s="123"/>
+      <c r="G15" s="122" t="s">
         <v>147</v>
       </c>
-      <c r="H15" s="144"/>
+      <c r="H15" s="124"/>
     </row>
     <row r="16" spans="1:8" ht="99" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="145">
+      <c r="A16" s="125">
         <v>4</v>
       </c>
-      <c r="B16" s="146" t="s">
+      <c r="B16" s="126" t="s">
         <v>148</v>
       </c>
-      <c r="C16" s="142" t="s">
+      <c r="C16" s="122" t="s">
         <v>29</v>
       </c>
-      <c r="D16" s="303" t="s">
+      <c r="D16" s="234" t="s">
         <v>149</v>
       </c>
-      <c r="E16" s="302"/>
-      <c r="F16" s="145"/>
-      <c r="G16" s="142" t="s">
+      <c r="E16" s="233"/>
+      <c r="F16" s="125"/>
+      <c r="G16" s="122" t="s">
         <v>29</v>
       </c>
-      <c r="H16" s="145"/>
+      <c r="H16" s="125"/>
     </row>
     <row r="17" spans="1:8" ht="78.75" x14ac:dyDescent="0.25">
-      <c r="A17" s="141">
+      <c r="A17" s="121">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="B17" s="142" t="s">
+      <c r="B17" s="122" t="s">
         <v>146</v>
       </c>
-      <c r="C17" s="142" t="s">
+      <c r="C17" s="122" t="s">
         <v>155</v>
       </c>
-      <c r="D17" s="303" t="s">
+      <c r="D17" s="234" t="s">
         <v>149</v>
       </c>
-      <c r="E17" s="302"/>
-      <c r="F17" s="145"/>
-      <c r="G17" s="142" t="s">
+      <c r="E17" s="233"/>
+      <c r="F17" s="125"/>
+      <c r="G17" s="122" t="s">
         <v>156</v>
       </c>
-      <c r="H17" s="145"/>
+      <c r="H17" s="125"/>
     </row>
     <row r="18" spans="1:8" ht="78.75" x14ac:dyDescent="0.25">
-      <c r="A18" s="145">
+      <c r="A18" s="125">
         <v>6</v>
       </c>
-      <c r="B18" s="146" t="s">
+      <c r="B18" s="126" t="s">
         <v>151</v>
       </c>
-      <c r="C18" s="142" t="s">
+      <c r="C18" s="122" t="s">
         <v>29</v>
       </c>
-      <c r="D18" s="303" t="s">
+      <c r="D18" s="234" t="s">
         <v>149</v>
       </c>
-      <c r="E18" s="302"/>
-      <c r="F18" s="145"/>
-      <c r="G18" s="142" t="s">
+      <c r="E18" s="233"/>
+      <c r="F18" s="125"/>
+      <c r="G18" s="122" t="s">
         <v>29</v>
       </c>
-      <c r="H18" s="145"/>
+      <c r="H18" s="125"/>
     </row>
     <row r="19" spans="1:8" ht="21" x14ac:dyDescent="0.25">
-      <c r="A19" s="141">
+      <c r="A19" s="121">
         <f t="shared" si="1"/>
         <v>7</v>
       </c>
-      <c r="B19" s="142" t="s">
+      <c r="B19" s="122" t="s">
         <v>146</v>
       </c>
-      <c r="C19" s="145" t="s">
-        <v>152</v>
-      </c>
-      <c r="D19" s="303" t="s">
+      <c r="C19" s="125" t="s">
+        <v>187</v>
+      </c>
+      <c r="D19" s="234" t="s">
         <v>149</v>
       </c>
-      <c r="E19" s="302"/>
-      <c r="F19" s="145"/>
-      <c r="G19" s="145" t="s">
-        <v>152</v>
-      </c>
-      <c r="H19" s="145"/>
+      <c r="E19" s="233"/>
+      <c r="F19" s="125"/>
+      <c r="G19" s="125" t="s">
+        <v>187</v>
+      </c>
+      <c r="H19" s="125"/>
     </row>
     <row r="20" spans="1:8" ht="78.75" x14ac:dyDescent="0.25">
-      <c r="A20" s="145">
+      <c r="A20" s="125">
         <v>8</v>
       </c>
-      <c r="B20" s="146" t="s">
+      <c r="B20" s="126" t="s">
         <v>154</v>
       </c>
-      <c r="C20" s="142" t="s">
+      <c r="C20" s="122" t="s">
         <v>29</v>
       </c>
-      <c r="D20" s="303" t="s">
+      <c r="D20" s="234" t="s">
         <v>149</v>
       </c>
-      <c r="E20" s="303"/>
-      <c r="F20" s="145"/>
-      <c r="G20" s="142" t="s">
+      <c r="E20" s="234"/>
+      <c r="F20" s="125"/>
+      <c r="G20" s="122" t="s">
         <v>29</v>
       </c>
-      <c r="H20" s="145"/>
+      <c r="H20" s="125"/>
     </row>
     <row r="21" spans="1:8" ht="63" x14ac:dyDescent="0.25">
-      <c r="A21" s="141">
+      <c r="A21" s="121">
         <f t="shared" si="1"/>
         <v>9</v>
       </c>
-      <c r="B21" s="142" t="s">
+      <c r="B21" s="122" t="s">
         <v>146</v>
       </c>
-      <c r="C21" s="145" t="s">
+      <c r="C21" s="125" t="s">
         <v>152</v>
       </c>
-      <c r="D21" s="303"/>
-      <c r="E21" s="303" t="s">
+      <c r="D21" s="234"/>
+      <c r="E21" s="234" t="s">
         <v>149</v>
       </c>
-      <c r="F21" s="145"/>
-      <c r="G21" s="147" t="s">
+      <c r="F21" s="125"/>
+      <c r="G21" s="127" t="s">
         <v>157</v>
       </c>
-      <c r="H21" s="145">
+      <c r="H21" s="125">
         <v>1</v>
       </c>
     </row>
     <row r="22" spans="1:8" ht="81" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="145">
+      <c r="A22" s="125">
         <v>10</v>
       </c>
-      <c r="B22" s="146" t="s">
+      <c r="B22" s="126" t="s">
         <v>159</v>
       </c>
-      <c r="C22" s="142" t="s">
+      <c r="C22" s="122" t="s">
         <v>29</v>
       </c>
-      <c r="D22" s="303" t="s">
+      <c r="D22" s="234" t="s">
         <v>149</v>
       </c>
-      <c r="E22" s="303"/>
-      <c r="F22" s="145"/>
-      <c r="G22" s="142" t="s">
+      <c r="E22" s="234"/>
+      <c r="F22" s="125"/>
+      <c r="G22" s="122" t="s">
         <v>29</v>
       </c>
-      <c r="H22" s="145"/>
+      <c r="H22" s="125"/>
     </row>
     <row r="23" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="141">
+      <c r="A23" s="121">
         <f t="shared" si="1"/>
         <v>11</v>
       </c>
-      <c r="B23" s="142" t="s">
+      <c r="B23" s="122" t="s">
         <v>146</v>
       </c>
-      <c r="C23" s="145" t="s">
-        <v>152</v>
-      </c>
-      <c r="D23" s="303" t="s">
+      <c r="C23" s="125" t="s">
+        <v>187</v>
+      </c>
+      <c r="D23" s="234" t="s">
         <v>149</v>
       </c>
-      <c r="E23" s="303"/>
-      <c r="F23" s="145"/>
-      <c r="G23" s="145" t="s">
-        <v>152</v>
-      </c>
-      <c r="H23" s="145"/>
+      <c r="E23" s="234"/>
+      <c r="F23" s="125"/>
+      <c r="G23" s="125" t="s">
+        <v>187</v>
+      </c>
+      <c r="H23" s="125"/>
     </row>
     <row r="24" spans="1:8" ht="80.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="145">
+      <c r="A24" s="125">
         <v>12</v>
       </c>
-      <c r="B24" s="146" t="s">
+      <c r="B24" s="126" t="s">
         <v>160</v>
       </c>
-      <c r="C24" s="142" t="s">
+      <c r="C24" s="122" t="s">
         <v>29</v>
       </c>
-      <c r="D24" s="303" t="s">
+      <c r="D24" s="234" t="s">
         <v>149</v>
       </c>
-      <c r="E24" s="303"/>
-      <c r="F24" s="145"/>
-      <c r="G24" s="142" t="s">
+      <c r="E24" s="234"/>
+      <c r="F24" s="125"/>
+      <c r="G24" s="122" t="s">
         <v>29</v>
       </c>
-      <c r="H24" s="145"/>
+      <c r="H24" s="125"/>
     </row>
     <row r="25" spans="1:8" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="141">
+      <c r="A25" s="121">
         <f t="shared" si="1"/>
         <v>13</v>
       </c>
-      <c r="B25" s="142" t="s">
+      <c r="B25" s="122" t="s">
         <v>161</v>
       </c>
-      <c r="C25" s="147" t="s">
+      <c r="C25" s="127" t="s">
         <v>162</v>
       </c>
-      <c r="D25" s="303" t="s">
+      <c r="D25" s="234" t="s">
         <v>27</v>
       </c>
-      <c r="E25" s="303"/>
-      <c r="F25" s="145"/>
-      <c r="G25" s="147" t="s">
+      <c r="E25" s="234"/>
+      <c r="F25" s="125"/>
+      <c r="G25" s="127" t="s">
         <v>162</v>
       </c>
-      <c r="H25" s="145"/>
+      <c r="H25" s="125"/>
     </row>
     <row r="26" spans="1:8" ht="51.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="145">
+      <c r="A26" s="125">
         <v>14</v>
       </c>
-      <c r="B26" s="146" t="s">
+      <c r="B26" s="126" t="s">
         <v>164</v>
       </c>
-      <c r="C26" s="142" t="s">
+      <c r="C26" s="122" t="s">
         <v>29</v>
       </c>
-      <c r="D26" s="303" t="s">
+      <c r="D26" s="234" t="s">
         <v>27</v>
       </c>
-      <c r="E26" s="303"/>
-      <c r="F26" s="145"/>
-      <c r="G26" s="142" t="s">
+      <c r="E26" s="234"/>
+      <c r="F26" s="125"/>
+      <c r="G26" s="122" t="s">
         <v>29</v>
       </c>
-      <c r="H26" s="145"/>
+      <c r="H26" s="125"/>
     </row>
     <row r="27" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="145">
+      <c r="A27" s="125">
         <v>15</v>
       </c>
-      <c r="B27" s="142" t="s">
+      <c r="B27" s="122" t="s">
         <v>161</v>
       </c>
-      <c r="C27" s="145" t="s">
+      <c r="C27" s="125" t="s">
         <v>165</v>
       </c>
-      <c r="D27" s="303" t="s">
+      <c r="D27" s="234" t="s">
         <v>149</v>
       </c>
-      <c r="E27" s="303"/>
-      <c r="F27" s="145"/>
-      <c r="G27" s="147" t="s">
+      <c r="E27" s="234"/>
+      <c r="F27" s="125"/>
+      <c r="G27" s="127" t="s">
         <v>165</v>
       </c>
-      <c r="H27" s="145"/>
+      <c r="H27" s="125"/>
     </row>
     <row r="28" spans="1:8" ht="44.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="141">
+      <c r="A28" s="121">
         <f t="shared" ref="A28" si="2">A27 + 1</f>
         <v>16</v>
       </c>
-      <c r="B28" s="146" t="s">
+      <c r="B28" s="126" t="s">
         <v>166</v>
       </c>
-      <c r="C28" s="142" t="s">
+      <c r="C28" s="122" t="s">
         <v>29</v>
       </c>
-      <c r="D28" s="303" t="s">
+      <c r="D28" s="234" t="s">
         <v>149</v>
       </c>
-      <c r="E28" s="303"/>
-      <c r="F28" s="145"/>
-      <c r="G28" s="142" t="s">
+      <c r="E28" s="234"/>
+      <c r="F28" s="125"/>
+      <c r="G28" s="122" t="s">
         <v>29</v>
       </c>
-      <c r="H28" s="145"/>
+      <c r="H28" s="125"/>
     </row>
     <row r="29" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="145">
+      <c r="A29" s="125">
         <v>17</v>
       </c>
-      <c r="B29" s="142" t="s">
+      <c r="B29" s="122" t="s">
         <v>161</v>
       </c>
-      <c r="C29" s="145" t="s">
+      <c r="C29" s="125" t="s">
         <v>167</v>
       </c>
-      <c r="D29" s="303" t="s">
+      <c r="D29" s="234" t="s">
         <v>149</v>
       </c>
-      <c r="E29" s="303"/>
-      <c r="F29" s="145"/>
-      <c r="G29" s="147" t="s">
+      <c r="E29" s="234"/>
+      <c r="F29" s="125"/>
+      <c r="G29" s="127" t="s">
         <v>167</v>
       </c>
-      <c r="H29" s="145"/>
+      <c r="H29" s="125"/>
     </row>
     <row r="30" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C30" s="14"/>
@@ -35724,70 +35738,70 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="156" t="s">
+      <c r="A1" s="288" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="157"/>
-      <c r="C1" s="158" t="s">
+      <c r="B1" s="289"/>
+      <c r="C1" s="129" t="s">
         <v>114</v>
       </c>
-      <c r="D1" s="157" t="s">
+      <c r="D1" s="289" t="s">
         <v>9</v>
       </c>
-      <c r="E1" s="157"/>
-      <c r="F1" s="157"/>
-      <c r="G1" s="167" t="s">
+      <c r="E1" s="289"/>
+      <c r="F1" s="289"/>
+      <c r="G1" s="135" t="s">
         <v>36</v>
       </c>
-      <c r="H1" s="170"/>
+      <c r="H1" s="138"/>
     </row>
     <row r="2" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A2" s="161" t="s">
+      <c r="A2" s="292" t="s">
         <v>10</v>
       </c>
-      <c r="B2" s="148"/>
-      <c r="C2" s="149" t="s">
+      <c r="B2" s="293"/>
+      <c r="C2" s="295" t="s">
         <v>168</v>
       </c>
-      <c r="D2" s="155" t="s">
+      <c r="D2" s="294" t="s">
         <v>11</v>
       </c>
-      <c r="E2" s="155"/>
-      <c r="F2" s="155"/>
-      <c r="G2" s="168" t="s">
+      <c r="E2" s="294"/>
+      <c r="F2" s="294"/>
+      <c r="G2" s="136" t="s">
         <v>35</v>
       </c>
-      <c r="H2" s="171"/>
+      <c r="H2" s="139"/>
     </row>
     <row r="3" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A3" s="161"/>
-      <c r="B3" s="148"/>
-      <c r="C3" s="151"/>
-      <c r="D3" s="155" t="s">
+      <c r="A3" s="292"/>
+      <c r="B3" s="293"/>
+      <c r="C3" s="296"/>
+      <c r="D3" s="294" t="s">
         <v>12</v>
       </c>
-      <c r="E3" s="155"/>
-      <c r="F3" s="155"/>
-      <c r="G3" s="169"/>
-      <c r="H3" s="171"/>
+      <c r="E3" s="294"/>
+      <c r="F3" s="294"/>
+      <c r="G3" s="137"/>
+      <c r="H3" s="139"/>
     </row>
     <row r="4" spans="1:8" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="163" t="s">
+      <c r="A4" s="290" t="s">
         <v>13</v>
       </c>
-      <c r="B4" s="164"/>
-      <c r="C4" s="165" t="s">
+      <c r="B4" s="291"/>
+      <c r="C4" s="133" t="s">
         <v>86</v>
       </c>
-      <c r="D4" s="164" t="s">
+      <c r="D4" s="291" t="s">
         <v>14</v>
       </c>
-      <c r="E4" s="164"/>
-      <c r="F4" s="164"/>
-      <c r="G4" s="210">
+      <c r="E4" s="291"/>
+      <c r="F4" s="291"/>
+      <c r="G4" s="169">
         <v>45795</v>
       </c>
-      <c r="H4" s="172"/>
+      <c r="H4" s="140"/>
     </row>
     <row r="5" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="16"/>
@@ -35800,42 +35814,42 @@
       <c r="H5" s="17"/>
     </row>
     <row r="6" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A6" s="182" t="s">
+      <c r="A6" s="297" t="s">
         <v>15</v>
       </c>
-      <c r="B6" s="183"/>
-      <c r="C6" s="118" t="s">
+      <c r="B6" s="298"/>
+      <c r="C6" s="98" t="s">
         <v>143</v>
       </c>
-      <c r="D6" s="173"/>
-      <c r="E6" s="174"/>
-      <c r="F6" s="174"/>
-      <c r="G6" s="174"/>
-      <c r="H6" s="175"/>
+      <c r="D6" s="141"/>
+      <c r="E6" s="142"/>
+      <c r="F6" s="142"/>
+      <c r="G6" s="142"/>
+      <c r="H6" s="143"/>
     </row>
     <row r="7" spans="1:8" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="184"/>
-      <c r="B7" s="185"/>
-      <c r="C7" s="186" t="s">
+      <c r="A7" s="299"/>
+      <c r="B7" s="300"/>
+      <c r="C7" s="150" t="s">
         <v>169</v>
       </c>
-      <c r="D7" s="176"/>
-      <c r="E7" s="177"/>
-      <c r="F7" s="177"/>
-      <c r="G7" s="177"/>
-      <c r="H7" s="178"/>
+      <c r="D7" s="144"/>
+      <c r="E7" s="145"/>
+      <c r="F7" s="145"/>
+      <c r="G7" s="145"/>
+      <c r="H7" s="146"/>
     </row>
     <row r="8" spans="1:8" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="187"/>
-      <c r="B8" s="188"/>
-      <c r="C8" s="189" t="s">
+      <c r="A8" s="301"/>
+      <c r="B8" s="302"/>
+      <c r="C8" s="151" t="s">
         <v>170</v>
       </c>
-      <c r="D8" s="179"/>
-      <c r="E8" s="180"/>
-      <c r="F8" s="180"/>
-      <c r="G8" s="180"/>
-      <c r="H8" s="181"/>
+      <c r="D8" s="147"/>
+      <c r="E8" s="148"/>
+      <c r="F8" s="148"/>
+      <c r="G8" s="148"/>
+      <c r="H8" s="149"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="16"/>
@@ -35858,219 +35872,220 @@
       <c r="H10" s="17"/>
     </row>
     <row r="11" spans="1:8" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="304">
+      <c r="A11" s="235">
         <v>8</v>
       </c>
-      <c r="B11" s="305" t="s">
+      <c r="B11" s="236" t="s">
         <v>16</v>
       </c>
-      <c r="C11" s="306" t="s">
+      <c r="C11" s="237" t="s">
         <v>17</v>
       </c>
-      <c r="D11" s="307">
+      <c r="D11" s="238">
         <v>5</v>
       </c>
-      <c r="E11" s="307">
+      <c r="E11" s="238">
         <v>3</v>
       </c>
-      <c r="F11" s="307">
+      <c r="F11" s="238">
         <v>0</v>
       </c>
-      <c r="G11" s="308" t="s">
+      <c r="G11" s="239" t="s">
         <v>18</v>
       </c>
-      <c r="H11" s="309">
+      <c r="H11" s="240">
         <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="310" t="s">
+      <c r="A12" s="241" t="s">
         <v>19</v>
       </c>
-      <c r="B12" s="305" t="s">
+      <c r="B12" s="236" t="s">
         <v>20</v>
       </c>
-      <c r="C12" s="311" t="s">
+      <c r="C12" s="242" t="s">
         <v>21</v>
       </c>
-      <c r="D12" s="307" t="s">
+      <c r="D12" s="238" t="s">
         <v>22</v>
       </c>
-      <c r="E12" s="307" t="s">
+      <c r="E12" s="238" t="s">
         <v>23</v>
       </c>
-      <c r="F12" s="307" t="s">
+      <c r="F12" s="238" t="s">
         <v>24</v>
       </c>
-      <c r="G12" s="312" t="s">
+      <c r="G12" s="243" t="s">
         <v>25</v>
       </c>
-      <c r="H12" s="313" t="s">
+      <c r="H12" s="244" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="79.900000000000006" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="190">
+      <c r="A13" s="152">
         <v>1</v>
       </c>
-      <c r="B13" s="191" t="s">
+      <c r="B13" s="153" t="s">
         <v>171</v>
       </c>
-      <c r="C13" s="192" t="s">
+      <c r="C13" s="154" t="s">
         <v>172</v>
       </c>
-      <c r="D13" s="193" t="s">
+      <c r="D13" s="155" t="s">
         <v>27</v>
       </c>
-      <c r="E13" s="194"/>
-      <c r="F13" s="194"/>
-      <c r="G13" s="192" t="s">
+      <c r="E13" s="156"/>
+      <c r="F13" s="156"/>
+      <c r="G13" s="154" t="s">
         <v>172</v>
       </c>
-      <c r="H13" s="195"/>
+      <c r="H13" s="157"/>
     </row>
     <row r="14" spans="1:8" ht="80.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="196">
+      <c r="A14" s="158">
         <v>2</v>
       </c>
-      <c r="B14" s="191" t="s">
+      <c r="B14" s="153" t="s">
         <v>173</v>
       </c>
-      <c r="C14" s="192" t="s">
+      <c r="C14" s="154" t="s">
         <v>174</v>
       </c>
-      <c r="D14" s="193" t="s">
+      <c r="D14" s="155" t="s">
         <v>149</v>
       </c>
-      <c r="E14" s="197"/>
-      <c r="F14" s="197"/>
-      <c r="G14" s="192" t="s">
+      <c r="E14" s="159"/>
+      <c r="F14" s="159"/>
+      <c r="G14" s="154" t="s">
         <v>174</v>
       </c>
-      <c r="H14" s="198"/>
+      <c r="H14" s="160"/>
     </row>
     <row r="15" spans="1:8" ht="70.900000000000006" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="196">
+      <c r="A15" s="158">
         <v>3</v>
       </c>
-      <c r="B15" s="191" t="s">
+      <c r="B15" s="153" t="s">
         <v>175</v>
       </c>
-      <c r="C15" s="192" t="s">
+      <c r="C15" s="154" t="s">
         <v>172</v>
       </c>
-      <c r="D15" s="199" t="s">
+      <c r="D15" s="161" t="s">
         <v>27</v>
       </c>
-      <c r="E15" s="200"/>
-      <c r="F15" s="200"/>
-      <c r="G15" s="192" t="s">
+      <c r="E15" s="162"/>
+      <c r="F15" s="162"/>
+      <c r="G15" s="154" t="s">
         <v>172</v>
       </c>
-      <c r="H15" s="201"/>
+      <c r="H15" s="163"/>
     </row>
     <row r="16" spans="1:8" ht="78.599999999999994" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="202">
+      <c r="A16" s="164">
         <v>4</v>
       </c>
-      <c r="B16" s="191" t="s">
+      <c r="B16" s="153" t="s">
         <v>173</v>
       </c>
-      <c r="C16" s="203" t="s">
+      <c r="C16" s="165" t="s">
         <v>187</v>
       </c>
-      <c r="D16" s="204" t="s">
+      <c r="D16" s="166" t="s">
         <v>149</v>
       </c>
-      <c r="E16" s="205"/>
-      <c r="F16" s="205"/>
-      <c r="G16" s="203" t="s">
+      <c r="E16" s="167"/>
+      <c r="F16" s="167"/>
+      <c r="G16" s="165" t="s">
         <v>187</v>
       </c>
-      <c r="H16" s="205"/>
+      <c r="H16" s="167"/>
     </row>
     <row r="17" spans="1:8" ht="78.599999999999994" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="202">
+      <c r="A17" s="164">
         <v>5</v>
       </c>
-      <c r="B17" s="191" t="s">
+      <c r="B17" s="153" t="s">
         <v>176</v>
       </c>
-      <c r="C17" s="192" t="s">
+      <c r="C17" s="154" t="s">
         <v>172</v>
       </c>
-      <c r="D17" s="206" t="s">
+      <c r="D17" s="168" t="s">
         <v>27</v>
       </c>
-      <c r="E17" s="205"/>
-      <c r="F17" s="205"/>
-      <c r="G17" s="192" t="s">
+      <c r="E17" s="167"/>
+      <c r="F17" s="167"/>
+      <c r="G17" s="154" t="s">
         <v>172</v>
       </c>
-      <c r="H17" s="205"/>
+      <c r="H17" s="167"/>
     </row>
     <row r="18" spans="1:8" ht="66" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="196">
+      <c r="A18" s="158">
         <v>6</v>
       </c>
-      <c r="B18" s="191" t="s">
+      <c r="B18" s="153" t="s">
         <v>173</v>
       </c>
-      <c r="C18" s="203" t="s">
+      <c r="C18" s="165" t="s">
         <v>187</v>
       </c>
-      <c r="D18" s="204" t="s">
+      <c r="D18" s="166" t="s">
         <v>149</v>
       </c>
-      <c r="E18" s="205"/>
-      <c r="F18" s="205"/>
-      <c r="G18" s="203" t="s">
+      <c r="E18" s="167"/>
+      <c r="F18" s="167"/>
+      <c r="G18" s="165" t="s">
         <v>187</v>
       </c>
-      <c r="H18" s="205"/>
+      <c r="H18" s="167"/>
     </row>
     <row r="19" spans="1:8" ht="120.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="196">
+      <c r="A19" s="158">
         <v>7</v>
       </c>
-      <c r="B19" s="191" t="s">
+      <c r="B19" s="153" t="s">
         <v>177</v>
       </c>
-      <c r="C19" s="192" t="s">
+      <c r="C19" s="154" t="s">
         <v>172</v>
       </c>
-      <c r="D19" s="204" t="s">
+      <c r="D19" s="166" t="s">
         <v>27</v>
       </c>
-      <c r="E19" s="205"/>
-      <c r="F19" s="205"/>
-      <c r="G19" s="192" t="s">
+      <c r="E19" s="167"/>
+      <c r="F19" s="167"/>
+      <c r="G19" s="154" t="s">
         <v>172</v>
       </c>
-      <c r="H19" s="205"/>
+      <c r="H19" s="167"/>
     </row>
     <row r="20" spans="1:8" ht="47.25" x14ac:dyDescent="0.25">
-      <c r="A20" s="196">
+      <c r="A20" s="158">
         <v>8</v>
       </c>
-      <c r="B20" s="191" t="s">
+      <c r="B20" s="153" t="s">
         <v>173</v>
       </c>
-      <c r="C20" s="203" t="s">
+      <c r="C20" s="165" t="s">
         <v>178</v>
       </c>
-      <c r="D20" s="204" t="s">
+      <c r="D20" s="166" t="s">
         <v>27</v>
       </c>
-      <c r="E20" s="205"/>
-      <c r="F20" s="205"/>
-      <c r="G20" s="203" t="s">
+      <c r="E20" s="167"/>
+      <c r="F20" s="167"/>
+      <c r="G20" s="165" t="s">
         <v>179</v>
       </c>
-      <c r="H20" s="205"/>
+      <c r="H20" s="167"/>
     </row>
   </sheetData>
   <mergeCells count="9">
+    <mergeCell ref="A6:B8"/>
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="A2:B3"/>
@@ -36079,7 +36094,6 @@
     <mergeCell ref="D3:F3"/>
     <mergeCell ref="D4:F4"/>
     <mergeCell ref="C2:C3"/>
-    <mergeCell ref="A6:B8"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -36097,72 +36111,72 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="182" t="s">
+      <c r="A1" s="297" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="183"/>
-      <c r="C1" s="218" t="s">
+      <c r="B1" s="298"/>
+      <c r="C1" s="171" t="s">
         <v>69</v>
       </c>
-      <c r="D1" s="211" t="s">
+      <c r="D1" s="312" t="s">
         <v>9</v>
       </c>
-      <c r="E1" s="212"/>
-      <c r="F1" s="213"/>
-      <c r="G1" s="159" t="s">
+      <c r="E1" s="313"/>
+      <c r="F1" s="314"/>
+      <c r="G1" s="130" t="s">
         <v>38</v>
       </c>
-      <c r="H1" s="160"/>
+      <c r="H1" s="131"/>
     </row>
     <row r="2" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A2" s="184" t="s">
+      <c r="A2" s="299" t="s">
         <v>10</v>
       </c>
-      <c r="B2" s="185"/>
-      <c r="C2" s="219" t="s">
+      <c r="B2" s="300"/>
+      <c r="C2" s="310" t="s">
         <v>180</v>
       </c>
-      <c r="D2" s="152" t="s">
+      <c r="D2" s="315" t="s">
         <v>11</v>
       </c>
-      <c r="E2" s="153"/>
-      <c r="F2" s="154"/>
-      <c r="G2" s="150" t="s">
+      <c r="E2" s="316"/>
+      <c r="F2" s="317"/>
+      <c r="G2" s="128" t="s">
         <v>35</v>
       </c>
-      <c r="H2" s="162"/>
+      <c r="H2" s="132"/>
     </row>
     <row r="3" spans="1:8" ht="48" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="184"/>
-      <c r="B3" s="185"/>
-      <c r="C3" s="220"/>
-      <c r="D3" s="207" t="s">
+      <c r="A3" s="299"/>
+      <c r="B3" s="300"/>
+      <c r="C3" s="311"/>
+      <c r="D3" s="318" t="s">
         <v>12</v>
       </c>
-      <c r="E3" s="208"/>
-      <c r="F3" s="209"/>
-      <c r="G3" s="239">
+      <c r="E3" s="319"/>
+      <c r="F3" s="320"/>
+      <c r="G3" s="186">
         <v>2</v>
       </c>
-      <c r="H3" s="162"/>
+      <c r="H3" s="132"/>
     </row>
     <row r="4" spans="1:8" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="163" t="s">
+      <c r="A4" s="290" t="s">
         <v>13</v>
       </c>
-      <c r="B4" s="164"/>
-      <c r="C4" s="221" t="s">
+      <c r="B4" s="291"/>
+      <c r="C4" s="172" t="s">
         <v>88</v>
       </c>
-      <c r="D4" s="214" t="s">
+      <c r="D4" s="303" t="s">
         <v>14</v>
       </c>
-      <c r="E4" s="215"/>
-      <c r="F4" s="216"/>
-      <c r="G4" s="217">
+      <c r="E4" s="304"/>
+      <c r="F4" s="305"/>
+      <c r="G4" s="170">
         <v>45795</v>
       </c>
-      <c r="H4" s="166"/>
+      <c r="H4" s="134"/>
     </row>
     <row r="5" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="16"/>
@@ -36175,30 +36189,30 @@
       <c r="H5" s="17"/>
     </row>
     <row r="6" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A6" s="230" t="s">
+      <c r="A6" s="306" t="s">
         <v>15</v>
       </c>
-      <c r="B6" s="231"/>
-      <c r="C6" s="118" t="s">
+      <c r="B6" s="307"/>
+      <c r="C6" s="98" t="s">
         <v>143</v>
       </c>
-      <c r="D6" s="223"/>
-      <c r="E6" s="224"/>
-      <c r="F6" s="224"/>
-      <c r="G6" s="224"/>
-      <c r="H6" s="225"/>
+      <c r="D6" s="174"/>
+      <c r="E6" s="175"/>
+      <c r="F6" s="175"/>
+      <c r="G6" s="175"/>
+      <c r="H6" s="176"/>
     </row>
     <row r="7" spans="1:8" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="232"/>
-      <c r="B7" s="233"/>
-      <c r="C7" s="226" t="s">
+      <c r="A7" s="308"/>
+      <c r="B7" s="309"/>
+      <c r="C7" s="177" t="s">
         <v>169</v>
       </c>
-      <c r="D7" s="227"/>
-      <c r="E7" s="228"/>
-      <c r="F7" s="228"/>
-      <c r="G7" s="228"/>
-      <c r="H7" s="229"/>
+      <c r="D7" s="178"/>
+      <c r="E7" s="179"/>
+      <c r="F7" s="179"/>
+      <c r="G7" s="179"/>
+      <c r="H7" s="180"/>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="16"/>
@@ -36231,176 +36245,176 @@
       <c r="H10" s="17"/>
     </row>
     <row r="11" spans="1:8" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="314">
+      <c r="A11" s="245">
         <v>6</v>
       </c>
-      <c r="B11" s="305" t="s">
+      <c r="B11" s="236" t="s">
         <v>16</v>
       </c>
-      <c r="C11" s="306" t="s">
+      <c r="C11" s="237" t="s">
         <v>17</v>
       </c>
-      <c r="D11" s="307">
+      <c r="D11" s="238">
         <v>5</v>
       </c>
-      <c r="E11" s="307">
+      <c r="E11" s="238">
         <v>1</v>
       </c>
-      <c r="F11" s="307">
+      <c r="F11" s="238">
         <v>0</v>
       </c>
-      <c r="G11" s="308" t="s">
+      <c r="G11" s="239" t="s">
         <v>18</v>
       </c>
-      <c r="H11" s="309">
+      <c r="H11" s="240">
         <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A12" s="315" t="s">
+      <c r="A12" s="246" t="s">
         <v>19</v>
       </c>
-      <c r="B12" s="316" t="s">
+      <c r="B12" s="247" t="s">
         <v>20</v>
       </c>
-      <c r="C12" s="316" t="s">
+      <c r="C12" s="247" t="s">
         <v>21</v>
       </c>
-      <c r="D12" s="317" t="s">
+      <c r="D12" s="248" t="s">
         <v>22</v>
       </c>
-      <c r="E12" s="317" t="s">
+      <c r="E12" s="248" t="s">
         <v>23</v>
       </c>
-      <c r="F12" s="317" t="s">
+      <c r="F12" s="248" t="s">
         <v>24</v>
       </c>
-      <c r="G12" s="318" t="s">
+      <c r="G12" s="249" t="s">
         <v>25</v>
       </c>
-      <c r="H12" s="319" t="s">
+      <c r="H12" s="250" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="59.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="234">
+      <c r="A13" s="181">
         <v>1</v>
       </c>
-      <c r="B13" s="235" t="s">
+      <c r="B13" s="182" t="s">
         <v>181</v>
       </c>
-      <c r="C13" s="235" t="s">
+      <c r="C13" s="182" t="s">
         <v>182</v>
       </c>
-      <c r="D13" s="236" t="s">
+      <c r="D13" s="183" t="s">
         <v>33</v>
       </c>
-      <c r="E13" s="235"/>
-      <c r="F13" s="237"/>
-      <c r="G13" s="235" t="s">
+      <c r="E13" s="182"/>
+      <c r="F13" s="184"/>
+      <c r="G13" s="182" t="s">
         <v>182</v>
       </c>
-      <c r="H13" s="235"/>
+      <c r="H13" s="182"/>
     </row>
     <row r="14" spans="1:8" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A14" s="234">
+      <c r="A14" s="181">
         <v>2</v>
       </c>
-      <c r="B14" s="235" t="s">
+      <c r="B14" s="182" t="s">
         <v>183</v>
       </c>
-      <c r="C14" s="235" t="s">
+      <c r="C14" s="182" t="s">
         <v>172</v>
       </c>
-      <c r="D14" s="236" t="s">
+      <c r="D14" s="183" t="s">
         <v>33</v>
       </c>
-      <c r="E14" s="235"/>
-      <c r="F14" s="237"/>
-      <c r="G14" s="235" t="s">
+      <c r="E14" s="182"/>
+      <c r="F14" s="184"/>
+      <c r="G14" s="182" t="s">
         <v>172</v>
       </c>
-      <c r="H14" s="235"/>
+      <c r="H14" s="182"/>
     </row>
     <row r="15" spans="1:8" ht="91.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="234">
+      <c r="A15" s="181">
         <v>3</v>
       </c>
-      <c r="B15" s="235" t="s">
+      <c r="B15" s="182" t="s">
         <v>184</v>
       </c>
-      <c r="C15" s="235" t="s">
+      <c r="C15" s="182" t="s">
         <v>185</v>
       </c>
-      <c r="D15" s="236" t="s">
+      <c r="D15" s="183" t="s">
         <v>33</v>
       </c>
-      <c r="E15" s="235"/>
-      <c r="F15" s="237"/>
-      <c r="G15" s="235" t="s">
+      <c r="E15" s="182"/>
+      <c r="F15" s="184"/>
+      <c r="G15" s="182" t="s">
         <v>185</v>
       </c>
-      <c r="H15" s="235"/>
+      <c r="H15" s="182"/>
     </row>
     <row r="16" spans="1:8" ht="76.150000000000006" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="234">
+      <c r="A16" s="181">
         <v>4</v>
       </c>
-      <c r="B16" s="235" t="s">
+      <c r="B16" s="182" t="s">
         <v>186</v>
       </c>
-      <c r="C16" s="235" t="s">
+      <c r="C16" s="182" t="s">
         <v>172</v>
       </c>
-      <c r="D16" s="236" t="s">
+      <c r="D16" s="183" t="s">
         <v>33</v>
       </c>
-      <c r="E16" s="235"/>
-      <c r="F16" s="237"/>
-      <c r="G16" s="235" t="s">
+      <c r="E16" s="182"/>
+      <c r="F16" s="184"/>
+      <c r="G16" s="182" t="s">
         <v>172</v>
       </c>
-      <c r="H16" s="235"/>
+      <c r="H16" s="182"/>
     </row>
     <row r="17" spans="1:8" ht="42.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="234">
+      <c r="A17" s="181">
         <v>5</v>
       </c>
-      <c r="B17" s="235" t="s">
+      <c r="B17" s="182" t="s">
         <v>184</v>
       </c>
-      <c r="C17" s="235" t="s">
+      <c r="C17" s="182" t="s">
         <v>187</v>
       </c>
-      <c r="D17" s="236" t="s">
+      <c r="D17" s="183" t="s">
         <v>33</v>
       </c>
-      <c r="E17" s="235"/>
-      <c r="F17" s="237"/>
-      <c r="G17" s="235" t="s">
+      <c r="E17" s="182"/>
+      <c r="F17" s="184"/>
+      <c r="G17" s="182" t="s">
         <v>187</v>
       </c>
-      <c r="H17" s="235"/>
+      <c r="H17" s="182"/>
     </row>
     <row r="18" spans="1:8" ht="144" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="196">
+      <c r="A18" s="158">
         <v>6</v>
       </c>
-      <c r="B18" s="235" t="s">
+      <c r="B18" s="182" t="s">
         <v>188</v>
       </c>
-      <c r="C18" s="238" t="s">
+      <c r="C18" s="185" t="s">
         <v>190</v>
       </c>
-      <c r="D18" s="205"/>
-      <c r="E18" s="204" t="s">
+      <c r="D18" s="167"/>
+      <c r="E18" s="166" t="s">
         <v>213</v>
       </c>
-      <c r="F18" s="205"/>
-      <c r="G18" s="238" t="s">
+      <c r="F18" s="167"/>
+      <c r="G18" s="185" t="s">
         <v>189</v>
       </c>
-      <c r="H18" s="202">
+      <c r="H18" s="164">
         <v>2</v>
       </c>
     </row>
@@ -36432,72 +36446,72 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="243" t="s">
+      <c r="A1" s="333" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="244"/>
-      <c r="C1" s="245" t="s">
+      <c r="B1" s="334"/>
+      <c r="C1" s="187" t="s">
         <v>191</v>
       </c>
-      <c r="D1" s="246" t="s">
+      <c r="D1" s="329" t="s">
         <v>9</v>
       </c>
-      <c r="E1" s="246"/>
-      <c r="F1" s="246"/>
-      <c r="G1" s="252" t="s">
+      <c r="E1" s="329"/>
+      <c r="F1" s="329"/>
+      <c r="G1" s="189" t="s">
         <v>39</v>
       </c>
-      <c r="H1" s="255"/>
+      <c r="H1" s="192"/>
     </row>
     <row r="2" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A2" s="247" t="s">
+      <c r="A2" s="335" t="s">
         <v>10</v>
       </c>
-      <c r="B2" s="241"/>
-      <c r="C2" s="242" t="s">
+      <c r="B2" s="336"/>
+      <c r="C2" s="332" t="s">
         <v>192</v>
       </c>
-      <c r="D2" s="240" t="s">
+      <c r="D2" s="330" t="s">
         <v>11</v>
       </c>
-      <c r="E2" s="240"/>
-      <c r="F2" s="240"/>
-      <c r="G2" s="253" t="s">
+      <c r="E2" s="330"/>
+      <c r="F2" s="330"/>
+      <c r="G2" s="190" t="s">
         <v>35</v>
       </c>
-      <c r="H2" s="256"/>
+      <c r="H2" s="193"/>
     </row>
     <row r="3" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A3" s="247"/>
-      <c r="B3" s="241"/>
-      <c r="C3" s="242"/>
-      <c r="D3" s="240" t="s">
+      <c r="A3" s="335"/>
+      <c r="B3" s="336"/>
+      <c r="C3" s="332"/>
+      <c r="D3" s="330" t="s">
         <v>12</v>
       </c>
-      <c r="E3" s="240"/>
-      <c r="F3" s="240"/>
-      <c r="G3" s="320">
+      <c r="E3" s="330"/>
+      <c r="F3" s="330"/>
+      <c r="G3" s="251">
         <v>3</v>
       </c>
-      <c r="H3" s="256"/>
+      <c r="H3" s="193"/>
     </row>
     <row r="4" spans="1:8" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="248" t="s">
+      <c r="A4" s="327" t="s">
         <v>13</v>
       </c>
-      <c r="B4" s="249"/>
-      <c r="C4" s="250" t="s">
+      <c r="B4" s="328"/>
+      <c r="C4" s="188" t="s">
         <v>85</v>
       </c>
-      <c r="D4" s="251" t="s">
+      <c r="D4" s="331" t="s">
         <v>14</v>
       </c>
-      <c r="E4" s="251"/>
-      <c r="F4" s="251"/>
-      <c r="G4" s="254">
+      <c r="E4" s="331"/>
+      <c r="F4" s="331"/>
+      <c r="G4" s="191">
         <v>45795</v>
       </c>
-      <c r="H4" s="257"/>
+      <c r="H4" s="194"/>
     </row>
     <row r="5" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="22"/>
@@ -36510,42 +36524,42 @@
       <c r="H5" s="23"/>
     </row>
     <row r="6" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A6" s="259" t="s">
+      <c r="A6" s="321" t="s">
         <v>15</v>
       </c>
-      <c r="B6" s="260"/>
-      <c r="C6" s="118" t="s">
+      <c r="B6" s="322"/>
+      <c r="C6" s="98" t="s">
         <v>143</v>
       </c>
-      <c r="D6" s="223"/>
-      <c r="E6" s="261"/>
-      <c r="F6" s="261"/>
-      <c r="G6" s="261"/>
-      <c r="H6" s="262"/>
+      <c r="D6" s="174"/>
+      <c r="E6" s="195"/>
+      <c r="F6" s="195"/>
+      <c r="G6" s="195"/>
+      <c r="H6" s="196"/>
     </row>
     <row r="7" spans="1:8" ht="17.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="263"/>
-      <c r="B7" s="258"/>
-      <c r="C7" s="186" t="s">
+      <c r="A7" s="323"/>
+      <c r="B7" s="324"/>
+      <c r="C7" s="150" t="s">
         <v>193</v>
       </c>
-      <c r="D7" s="222"/>
-      <c r="E7" s="264"/>
-      <c r="F7" s="264"/>
-      <c r="G7" s="264"/>
-      <c r="H7" s="265"/>
+      <c r="D7" s="173"/>
+      <c r="E7" s="197"/>
+      <c r="F7" s="197"/>
+      <c r="G7" s="197"/>
+      <c r="H7" s="198"/>
     </row>
     <row r="8" spans="1:8" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="266"/>
-      <c r="B8" s="267"/>
-      <c r="C8" s="268" t="s">
+      <c r="A8" s="325"/>
+      <c r="B8" s="326"/>
+      <c r="C8" s="199" t="s">
         <v>197</v>
       </c>
-      <c r="D8" s="269"/>
-      <c r="E8" s="270"/>
-      <c r="F8" s="270"/>
-      <c r="G8" s="270"/>
-      <c r="H8" s="271"/>
+      <c r="D8" s="200"/>
+      <c r="E8" s="201"/>
+      <c r="F8" s="201"/>
+      <c r="G8" s="201"/>
+      <c r="H8" s="202"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="22"/>
@@ -36568,158 +36582,158 @@
       <c r="H10" s="23"/>
     </row>
     <row r="11" spans="1:8" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="272">
+      <c r="A11" s="203">
         <v>4</v>
       </c>
-      <c r="B11" s="273" t="s">
+      <c r="B11" s="204" t="s">
         <v>16</v>
       </c>
-      <c r="C11" s="274" t="s">
+      <c r="C11" s="205" t="s">
         <v>17</v>
       </c>
-      <c r="D11" s="275">
+      <c r="D11" s="206">
         <v>3</v>
       </c>
-      <c r="E11" s="275">
+      <c r="E11" s="206">
         <v>1</v>
       </c>
-      <c r="F11" s="275">
+      <c r="F11" s="206">
         <v>0</v>
       </c>
-      <c r="G11" s="276" t="s">
+      <c r="G11" s="207" t="s">
         <v>18</v>
       </c>
-      <c r="H11" s="277">
+      <c r="H11" s="208">
         <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="278" t="s">
+      <c r="A12" s="209" t="s">
         <v>19</v>
       </c>
-      <c r="B12" s="279" t="s">
+      <c r="B12" s="210" t="s">
         <v>20</v>
       </c>
-      <c r="C12" s="279" t="s">
+      <c r="C12" s="210" t="s">
         <v>21</v>
       </c>
-      <c r="D12" s="275" t="s">
+      <c r="D12" s="206" t="s">
         <v>22</v>
       </c>
-      <c r="E12" s="275" t="s">
+      <c r="E12" s="206" t="s">
         <v>23</v>
       </c>
-      <c r="F12" s="275" t="s">
+      <c r="F12" s="206" t="s">
         <v>24</v>
       </c>
-      <c r="G12" s="280" t="s">
+      <c r="G12" s="211" t="s">
         <v>25</v>
       </c>
-      <c r="H12" s="281" t="s">
+      <c r="H12" s="212" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="72.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="297">
+      <c r="A13" s="228">
         <v>1</v>
       </c>
-      <c r="B13" s="282" t="s">
+      <c r="B13" s="213" t="s">
         <v>194</v>
       </c>
-      <c r="C13" s="282" t="s">
+      <c r="C13" s="213" t="s">
         <v>195</v>
       </c>
-      <c r="D13" s="292" t="s">
+      <c r="D13" s="223" t="s">
         <v>27</v>
       </c>
-      <c r="E13" s="292"/>
-      <c r="F13" s="283"/>
-      <c r="G13" s="282" t="s">
+      <c r="E13" s="223"/>
+      <c r="F13" s="214"/>
+      <c r="G13" s="213" t="s">
         <v>195</v>
       </c>
-      <c r="H13" s="284"/>
+      <c r="H13" s="215"/>
     </row>
     <row r="14" spans="1:8" ht="147.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="298">
+      <c r="A14" s="229">
         <v>2</v>
       </c>
-      <c r="B14" s="282" t="s">
+      <c r="B14" s="213" t="s">
         <v>196</v>
       </c>
-      <c r="C14" s="282" t="s">
+      <c r="C14" s="213" t="s">
         <v>198</v>
       </c>
-      <c r="D14" s="292" t="s">
+      <c r="D14" s="223" t="s">
         <v>27</v>
       </c>
-      <c r="E14" s="293"/>
-      <c r="F14" s="285"/>
-      <c r="G14" s="282" t="s">
+      <c r="E14" s="224"/>
+      <c r="F14" s="216"/>
+      <c r="G14" s="213" t="s">
         <v>198</v>
       </c>
-      <c r="H14" s="286"/>
+      <c r="H14" s="217"/>
     </row>
     <row r="15" spans="1:8" ht="116.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="299">
+      <c r="A15" s="230">
         <v>3</v>
       </c>
-      <c r="B15" s="287" t="s">
+      <c r="B15" s="218" t="s">
         <v>200</v>
       </c>
-      <c r="C15" s="287" t="s">
+      <c r="C15" s="218" t="s">
         <v>199</v>
       </c>
-      <c r="D15" s="294"/>
-      <c r="E15" s="295" t="s">
+      <c r="D15" s="225"/>
+      <c r="E15" s="226" t="s">
         <v>149</v>
       </c>
-      <c r="F15" s="288"/>
-      <c r="G15" s="287" t="s">
+      <c r="F15" s="219"/>
+      <c r="G15" s="218" t="s">
         <v>201</v>
       </c>
-      <c r="H15" s="289">
+      <c r="H15" s="220">
         <v>3</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="108" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="300">
+      <c r="A16" s="231">
         <v>4</v>
       </c>
-      <c r="B16" s="290" t="s">
+      <c r="B16" s="221" t="s">
         <v>202</v>
       </c>
-      <c r="C16" s="290" t="s">
+      <c r="C16" s="221" t="s">
         <v>204</v>
       </c>
-      <c r="D16" s="296" t="s">
+      <c r="D16" s="227" t="s">
         <v>27</v>
       </c>
-      <c r="E16" s="296"/>
-      <c r="F16" s="291"/>
-      <c r="G16" s="290" t="s">
+      <c r="E16" s="227"/>
+      <c r="F16" s="222"/>
+      <c r="G16" s="221" t="s">
         <v>203</v>
       </c>
-      <c r="H16" s="291"/>
+      <c r="H16" s="222"/>
     </row>
     <row r="17" spans="1:8" ht="76.900000000000006" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="70"/>
-      <c r="B17" s="71"/>
-      <c r="C17" s="71"/>
-      <c r="D17" s="72"/>
-      <c r="E17" s="72"/>
-      <c r="F17" s="72"/>
-      <c r="G17" s="71"/>
-      <c r="H17" s="72"/>
+      <c r="A17" s="66"/>
+      <c r="B17" s="67"/>
+      <c r="C17" s="67"/>
+      <c r="D17" s="68"/>
+      <c r="E17" s="68"/>
+      <c r="F17" s="68"/>
+      <c r="G17" s="67"/>
+      <c r="H17" s="68"/>
     </row>
     <row r="18" spans="1:8" ht="66.599999999999994" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="70"/>
-      <c r="B18" s="71"/>
-      <c r="C18" s="71"/>
-      <c r="D18" s="72"/>
-      <c r="E18" s="72"/>
-      <c r="F18" s="72"/>
-      <c r="G18" s="71"/>
-      <c r="H18" s="72"/>
+      <c r="A18" s="66"/>
+      <c r="B18" s="67"/>
+      <c r="C18" s="67"/>
+      <c r="D18" s="68"/>
+      <c r="E18" s="68"/>
+      <c r="F18" s="68"/>
+      <c r="G18" s="67"/>
+      <c r="H18" s="68"/>
     </row>
   </sheetData>
   <mergeCells count="9">

--- a/Стратегия тестирования.xlsx
+++ b/Стратегия тестирования.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="-105" windowWidth="20730" windowHeight="11760" tabRatio="397" firstSheet="2" activeTab="6"/>
+    <workbookView xWindow="-105" yWindow="-105" windowWidth="20730" windowHeight="11760" tabRatio="397" firstSheet="1" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="Тест-план" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="422" uniqueCount="219">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="422" uniqueCount="217">
   <si>
     <t>Цели доработки</t>
   </si>
@@ -499,12 +499,6 @@
     <t>На странице регистрации ввести Login: NewUser, Nickname: newUser, Password: ok, Check Pass.: ok, Email: testmail@gmail.com</t>
   </si>
   <si>
-    <t>Кнопка не активна</t>
-  </si>
-  <si>
-    <t>Кнопка регистрации не активна</t>
-  </si>
-  <si>
     <t>На странице регистрации ввести Login: NewUser, Nickname: newUser, Password: qwerty12345, Check Pass. : qwerty12345, Email: testmail</t>
   </si>
   <si>
@@ -775,11 +769,19 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="36" x14ac:knownFonts="1">
+  <fonts count="37" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
@@ -2084,231 +2086,231 @@
   </borders>
   <cellStyleXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="9"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="9"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="9"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="9"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="9" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="9"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="9"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="9"/>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="9" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="9"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="9"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="9" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="9"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="9" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="9"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="9" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="9"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="9"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="9"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="9"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="9"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="9"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="9" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="9"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="9" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="9"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="9" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="9"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="9"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="9" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="9"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="9"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="9" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="9"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="9"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="9"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="9"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="9"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="9"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="9" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="9" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="9" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9"/>
   </cellStyleXfs>
-  <cellXfs count="338">
+  <cellXfs count="339">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" xfId="5" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" xfId="5" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" xfId="5" applyFont="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" xfId="5" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" xfId="5" applyFont="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="9" xfId="5" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" xfId="5" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" xfId="5" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" xfId="5" applyFont="1"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="9" xfId="11"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="11" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="11" applyFont="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" xfId="5" applyFont="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="9" xfId="11"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="9" xfId="11" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="11" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="9" xfId="11" applyFont="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="11" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="9" xfId="11" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="9" xfId="20"/>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="9" xfId="20"/>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="24" xfId="29" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="24" xfId="29" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="29" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="29" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="24" xfId="29" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="24" xfId="29" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="29" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="29" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="29" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="29" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="9" xfId="29" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="9" xfId="29" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="29" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="29" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="9" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="29" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="29" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="24" xfId="29" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="24" xfId="29" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="24" xfId="29" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="24" xfId="29" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="24" xfId="29" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="8" borderId="24" xfId="29" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -2317,663 +2319,666 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="29" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="29" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="24" xfId="29" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="24" xfId="29" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="9" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="28" fillId="9" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="9" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="29" fillId="9" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="9" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="29" fillId="9" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="9" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="29" fillId="9" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="9" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="28" fillId="9" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="28" fillId="9" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="29" fillId="9" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="9" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="29" fillId="9" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="29" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="9" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="28" fillId="9" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="28" fillId="9" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="29" fillId="9" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="9" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="29" fillId="9" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="9" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="29" fillId="9" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="28" fillId="0" borderId="58" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="29" fillId="0" borderId="58" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="9" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="28" fillId="9" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="5" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="28" fillId="5" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="29" fillId="5" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="5" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="27" fillId="5" borderId="63" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="27" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="32" fillId="5" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="28" fillId="5" borderId="63" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="28" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="28" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="27" fillId="5" borderId="64" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="27" fillId="5" borderId="65" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="65" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="32" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="28" fillId="5" borderId="64" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="28" fillId="5" borderId="65" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="29" fillId="5" borderId="65" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="5" borderId="65" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="27" fillId="5" borderId="66" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="28" fillId="9" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="32" fillId="5" borderId="65" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="28" fillId="5" borderId="66" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="29" fillId="9" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="9" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="28" fillId="9" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="29" fillId="9" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="29" fillId="9" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="9" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="29" fillId="9" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="9" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="29" fillId="9" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="9" fontId="28" fillId="9" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="28" fillId="9" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="29" fillId="9" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="29" fillId="9" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="9" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="28" fillId="9" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="29" fillId="9" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="29" fillId="9" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="9" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="28" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="29" fillId="9" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="29" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="24" xfId="29" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="24" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="70" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="70" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="9" borderId="71" xfId="5" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="28" fillId="9" borderId="73" xfId="5" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="57" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="9" borderId="75" xfId="5" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="76" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="41" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="41" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="9" borderId="36" xfId="5" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="28" fillId="9" borderId="54" xfId="5" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="28" fillId="9" borderId="60" xfId="5" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="20" fillId="5" borderId="62" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="5" borderId="62" xfId="5" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="5" borderId="63" xfId="5" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="5" borderId="9" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="5" borderId="9" xfId="5" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="5" borderId="64" xfId="5" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="20" fillId="5" borderId="65" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="5" borderId="65" xfId="5" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="5" borderId="66" xfId="5" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="28" fillId="5" borderId="9" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="5" borderId="65" xfId="5" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="40" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="24" xfId="29" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="8" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="2" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="6" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="6" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="20" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="24" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="2" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="22" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="25" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="4" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="26" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="24" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="12" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="24" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="24" xfId="5" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="24" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="29" fillId="0" borderId="58" xfId="5" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="29" fillId="0" borderId="57" xfId="5" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="78" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="56" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="5" borderId="9" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="5" borderId="62" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="5" borderId="62" xfId="5" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="28" fillId="5" borderId="63" xfId="5" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="28" fillId="5" borderId="65" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="5" borderId="65" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="5" borderId="65" xfId="5" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="28" fillId="5" borderId="66" xfId="5" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="24" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="24" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="24" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="24" xfId="6" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="24" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="24" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="70" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="57" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="76" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="41" xfId="11" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="29" fillId="0" borderId="58" xfId="11" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="9" borderId="36" xfId="11" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="28" fillId="9" borderId="54" xfId="11" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="28" fillId="9" borderId="60" xfId="11" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="32" fillId="5" borderId="62" xfId="11" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="28" fillId="5" borderId="63" xfId="11" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="32" fillId="5" borderId="9" xfId="11" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="28" fillId="5" borderId="64" xfId="11" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="28" fillId="5" borderId="65" xfId="11" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="29" fillId="5" borderId="65" xfId="11" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="5" borderId="65" xfId="11" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="28" fillId="5" borderId="66" xfId="11" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="29" fillId="9" borderId="13" xfId="11" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="9" borderId="14" xfId="11" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="29" fillId="9" borderId="15" xfId="11" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="9" borderId="15" xfId="11" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="9" borderId="16" xfId="11" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="9" fontId="29" fillId="9" borderId="17" xfId="11" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="29" fillId="9" borderId="18" xfId="11" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="9" borderId="15" xfId="11" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="29" fillId="9" borderId="16" xfId="11" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="29" fillId="9" borderId="17" xfId="11" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="2" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="6" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="20" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="2" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="22" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="4" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="4" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="26" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="24" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="24" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="6" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="2" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="25" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="4" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="24" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="19" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="21" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="43" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="24" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="31" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="24" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="9" borderId="77" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="9" borderId="14" xfId="5" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="29" fillId="9" borderId="15" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="9" borderId="15" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="9" borderId="16" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="9" fontId="29" fillId="9" borderId="17" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="29" fillId="9" borderId="33" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="9" borderId="15" xfId="5" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="29" fillId="9" borderId="16" xfId="5" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="29" fillId="9" borderId="17" xfId="5" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="29" fillId="9" borderId="13" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="9" borderId="44" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="9" borderId="45" xfId="5" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="29" fillId="9" borderId="45" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="9" borderId="46" xfId="5" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="29" fillId="9" borderId="10" xfId="5" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="41" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="70" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="34" fillId="8" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="8" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="8" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="8" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="29" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="24" xfId="29" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="41" xfId="29" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="42" xfId="29" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="39" xfId="29" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="9" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="9" borderId="67" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="9" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="9" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="9" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="9" borderId="68" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="9" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="8" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="29" fillId="9" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="8" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="70" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="61" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="9" borderId="71" xfId="5" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="27" fillId="9" borderId="73" xfId="5" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="57" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
+    <xf numFmtId="0" fontId="29" fillId="9" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="9" borderId="75" xfId="5" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="76" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="29" fillId="9" borderId="59" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="41" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="29" fillId="9" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="41" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="29" fillId="9" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="9" borderId="36" xfId="5" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="27" fillId="9" borderId="54" xfId="5" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="27" fillId="9" borderId="60" xfId="5" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="19" fillId="5" borderId="62" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="29" fillId="9" borderId="69" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="9" borderId="70" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="9" borderId="72" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="9" borderId="24" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="9" borderId="74" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="9" borderId="57" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="9" borderId="69" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="9" borderId="70" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="9" borderId="74" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="9" borderId="57" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="9" borderId="72" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="9" borderId="24" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="9" borderId="24" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="24" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="24" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="9" borderId="58" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="9" borderId="59" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="9" borderId="56" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="9" borderId="35" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="9" borderId="67" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="9" borderId="38" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="9" borderId="68" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="39" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="39" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="29" fillId="9" borderId="76" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="9" borderId="79" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="9" borderId="78" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="9" borderId="41" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="9" borderId="42" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="9" borderId="39" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="9" borderId="41" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="9" borderId="42" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="9" borderId="39" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="9" borderId="35" xfId="11" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="9" borderId="62" xfId="11" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="9" borderId="37" xfId="11" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="9" borderId="9" xfId="11" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="9" borderId="38" xfId="11" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="9" borderId="65" xfId="11" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="9" borderId="74" xfId="11" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="5" borderId="62" xfId="5" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="63" xfId="5" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="9" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="5" borderId="9" xfId="5" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="64" xfId="5" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="19" fillId="5" borderId="65" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="29" fillId="9" borderId="57" xfId="11" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="5" borderId="65" xfId="5" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="66" xfId="5" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="27" fillId="5" borderId="9" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="5" borderId="65" xfId="5" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="40" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="8" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="2" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="6" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="6" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="20" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="24" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="2" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="22" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="25" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="4" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="26" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="24" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="12" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="24" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="24" xfId="5" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="24" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="28" fillId="0" borderId="58" xfId="5" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="28" fillId="0" borderId="57" xfId="5" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="78" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="56" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="5" borderId="9" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="62" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="5" borderId="62" xfId="5" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="27" fillId="5" borderId="63" xfId="5" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="27" fillId="5" borderId="65" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="5" borderId="65" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="5" borderId="65" xfId="5" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="27" fillId="5" borderId="66" xfId="5" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="24" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="24" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="24" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="24" xfId="6" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="24" xfId="9" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="24" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="70" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="57" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="76" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="41" xfId="11" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="28" fillId="0" borderId="58" xfId="11" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="9" borderId="36" xfId="11" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="27" fillId="9" borderId="54" xfId="11" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="27" fillId="9" borderId="60" xfId="11" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="31" fillId="5" borderId="62" xfId="11" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="27" fillId="5" borderId="63" xfId="11" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="31" fillId="5" borderId="9" xfId="11" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="27" fillId="5" borderId="64" xfId="11" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="27" fillId="5" borderId="65" xfId="11" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="65" xfId="11" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="5" borderId="65" xfId="11" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="27" fillId="5" borderId="66" xfId="11" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="28" fillId="9" borderId="13" xfId="11" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="9" borderId="14" xfId="11" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="28" fillId="9" borderId="15" xfId="11" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="29" fillId="9" borderId="70" xfId="11" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="9" borderId="15" xfId="11" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="9" borderId="16" xfId="11" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="29" fillId="9" borderId="24" xfId="11" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="9" fontId="28" fillId="9" borderId="17" xfId="11" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="28" fillId="9" borderId="18" xfId="11" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="9" borderId="15" xfId="11" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="28" fillId="9" borderId="16" xfId="11" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="28" fillId="9" borderId="17" xfId="11" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="2" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="6" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="20" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="2" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="22" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="4" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="4" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="26" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="24" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="29" fillId="9" borderId="57" xfId="11" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="0" borderId="24" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="6" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="2" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="25" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="4" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="24" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="19" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="21" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="43" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="24" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="9" borderId="77" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="29" fillId="9" borderId="69" xfId="11" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="9" borderId="14" xfId="5" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="28" fillId="9" borderId="15" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="9" borderId="15" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="29" fillId="9" borderId="70" xfId="11" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="9" borderId="16" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="9" fontId="28" fillId="9" borderId="17" xfId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="28" fillId="9" borderId="33" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="9" borderId="15" xfId="5" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="28" fillId="9" borderId="16" xfId="5" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="28" fillId="9" borderId="17" xfId="5" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="28" fillId="9" borderId="13" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="9" borderId="44" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="9" borderId="45" xfId="5" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="28" fillId="9" borderId="45" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="9" borderId="46" xfId="5" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="28" fillId="9" borderId="10" xfId="5" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="41" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="33" fillId="8" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="8" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="8" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="8" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="24" xfId="29" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="41" xfId="29" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="42" xfId="29" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="39" xfId="29" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="9" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="9" borderId="67" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="9" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="9" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="9" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="9" borderId="68" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="9" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="8" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="28" fillId="9" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="8" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="61" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="9" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="9" borderId="59" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="9" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="9" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="9" borderId="69" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="9" borderId="70" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="9" borderId="74" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="9" borderId="57" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="9" borderId="72" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="9" borderId="24" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="9" borderId="24" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="24" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="24" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="9" borderId="69" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="9" borderId="70" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="9" borderId="72" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="9" borderId="24" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="9" borderId="74" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="9" borderId="57" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="9" borderId="58" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="9" borderId="59" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="9" borderId="56" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="9" borderId="35" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="9" borderId="67" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="9" borderId="38" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="9" borderId="68" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="39" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="39" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="28" fillId="9" borderId="76" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="9" borderId="79" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="9" borderId="78" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="9" borderId="41" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="9" borderId="42" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="9" borderId="39" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="9" borderId="41" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="9" borderId="42" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="9" borderId="39" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="9" borderId="35" xfId="11" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="9" borderId="62" xfId="11" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="9" borderId="37" xfId="11" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="9" borderId="9" xfId="11" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="9" borderId="38" xfId="11" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="9" borderId="65" xfId="11" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="9" borderId="74" xfId="11" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="9" borderId="57" xfId="11" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="9" borderId="70" xfId="11" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="9" borderId="24" xfId="11" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="9" borderId="57" xfId="11" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="24" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="9" borderId="69" xfId="11" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="9" borderId="70" xfId="11" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="9" borderId="72" xfId="11" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="29" fillId="9" borderId="72" xfId="11" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="9" borderId="24" xfId="11" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="29" fillId="9" borderId="24" xfId="11" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="24" xfId="29" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -3311,7 +3316,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -3639,7 +3644,7 @@
         <v>0.5</v>
       </c>
       <c r="E10" s="49" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="F10" s="54" t="s">
         <v>86</v>
@@ -3682,7 +3687,7 @@
         <v>0.5</v>
       </c>
       <c r="E11" s="50" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="F11" s="54" t="s">
         <v>86</v>
@@ -3725,7 +3730,7 @@
         <v>0.2</v>
       </c>
       <c r="E12" s="49" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="F12" s="54" t="s">
         <v>86</v>
@@ -3768,7 +3773,7 @@
         <v>0.5</v>
       </c>
       <c r="E13" s="51" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="F13" s="55" t="s">
         <v>85</v>
@@ -3811,7 +3816,7 @@
         <v>0.5</v>
       </c>
       <c r="E14" s="52" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="F14" s="52" t="s">
         <v>85</v>
@@ -3854,7 +3859,7 @@
         <v>0.3</v>
       </c>
       <c r="E15" s="56" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="F15" s="56" t="s">
         <v>85</v>
@@ -3897,7 +3902,7 @@
         <v>0.2</v>
       </c>
       <c r="E16" s="56" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="F16" s="56" t="s">
         <v>85</v>
@@ -3941,7 +3946,7 @@
         <v>0.2</v>
       </c>
       <c r="E17" s="56" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="F17" s="56" t="s">
         <v>86</v>
@@ -3985,7 +3990,7 @@
         <v>0.5</v>
       </c>
       <c r="E18" s="52" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="F18" s="52" t="s">
         <v>86</v>
@@ -33535,19 +33540,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="263" t="s">
+      <c r="A1" s="264" t="s">
         <v>90</v>
       </c>
-      <c r="B1" s="264"/>
-      <c r="C1" s="264"/>
-      <c r="D1" s="264"/>
-      <c r="E1" s="265"/>
+      <c r="B1" s="265"/>
+      <c r="C1" s="265"/>
+      <c r="D1" s="265"/>
+      <c r="E1" s="266"/>
       <c r="F1" s="60"/>
-      <c r="G1" s="262" t="s">
+      <c r="G1" s="263" t="s">
         <v>92</v>
       </c>
-      <c r="H1" s="262"/>
-      <c r="I1" s="262"/>
+      <c r="H1" s="263"/>
+      <c r="I1" s="263"/>
     </row>
     <row r="2" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="73" t="s">
@@ -33621,11 +33626,11 @@
       <c r="B5" s="58" t="s">
         <v>107</v>
       </c>
-      <c r="C5" s="337" t="s">
-        <v>218</v>
-      </c>
-      <c r="D5" s="337" t="s">
-        <v>218</v>
+      <c r="C5" s="262" t="s">
+        <v>216</v>
+      </c>
+      <c r="D5" s="262" t="s">
+        <v>216</v>
       </c>
       <c r="E5" s="70"/>
       <c r="F5" s="60"/>
@@ -33640,11 +33645,11 @@
       <c r="B6" s="58" t="s">
         <v>108</v>
       </c>
-      <c r="C6" s="61" t="s">
-        <v>153</v>
+      <c r="C6" s="338" t="s">
+        <v>216</v>
       </c>
       <c r="D6" s="61" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="E6" s="72">
         <v>1</v>
@@ -33654,7 +33659,7 @@
         <v>1</v>
       </c>
       <c r="H6" s="58" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="I6" s="78" t="s">
         <v>101</v>
@@ -33667,11 +33672,11 @@
       <c r="B7" s="58" t="s">
         <v>110</v>
       </c>
-      <c r="C7" s="337" t="s">
-        <v>218</v>
-      </c>
-      <c r="D7" s="337" t="s">
-        <v>218</v>
+      <c r="C7" s="262" t="s">
+        <v>216</v>
+      </c>
+      <c r="D7" s="262" t="s">
+        <v>216</v>
       </c>
       <c r="E7" s="70"/>
       <c r="F7" s="60"/>
@@ -33842,7 +33847,7 @@
         <v>139</v>
       </c>
       <c r="D16" s="61" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="E16" s="57">
         <v>2</v>
@@ -33852,7 +33857,7 @@
         <v>2</v>
       </c>
       <c r="H16" s="58" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="I16" s="78" t="s">
         <v>101</v>
@@ -33888,7 +33893,7 @@
         <v>141</v>
       </c>
       <c r="D18" s="69" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="E18" s="57">
         <v>3</v>
@@ -33898,7 +33903,7 @@
         <v>3</v>
       </c>
       <c r="H18" s="56" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="I18" s="43" t="s">
         <v>101</v>
@@ -33915,7 +33920,7 @@
         <v>142</v>
       </c>
       <c r="D19" s="61" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="E19" s="70"/>
       <c r="F19"/>
@@ -33995,11 +34000,11 @@
       <c r="A1" s="258" t="s">
         <v>40</v>
       </c>
-      <c r="B1" s="266" t="s">
-        <v>214</v>
-      </c>
-      <c r="C1" s="267"/>
-      <c r="D1" s="268"/>
+      <c r="B1" s="267" t="s">
+        <v>212</v>
+      </c>
+      <c r="C1" s="268"/>
+      <c r="D1" s="269"/>
     </row>
     <row r="2" spans="1:4" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="259" t="s">
@@ -34020,7 +34025,7 @@
         <v>42</v>
       </c>
       <c r="B3" s="256" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="C3" s="260" t="s">
         <v>43</v>
@@ -34038,7 +34043,7 @@
         <v>44</v>
       </c>
       <c r="D4" s="254" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -34129,11 +34134,11 @@
       <c r="A12" s="261" t="s">
         <v>61</v>
       </c>
-      <c r="B12" s="269" t="s">
-        <v>217</v>
-      </c>
-      <c r="C12" s="270"/>
-      <c r="D12" s="271"/>
+      <c r="B12" s="270" t="s">
+        <v>215</v>
+      </c>
+      <c r="C12" s="271"/>
+      <c r="D12" s="272"/>
     </row>
     <row r="18" spans="6:7" x14ac:dyDescent="0.25">
       <c r="F18" s="26"/>
@@ -34213,11 +34218,11 @@
       <c r="H1" s="85"/>
     </row>
     <row r="2" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A2" s="278"/>
-      <c r="B2" s="280" t="s">
+      <c r="A2" s="279"/>
+      <c r="B2" s="281" t="s">
         <v>10</v>
       </c>
-      <c r="C2" s="282" t="s">
+      <c r="C2" s="283" t="s">
         <v>89</v>
       </c>
       <c r="D2" s="86"/>
@@ -34231,9 +34236,9 @@
       <c r="H2" s="90"/>
     </row>
     <row r="3" spans="1:8" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="279"/>
-      <c r="B3" s="281"/>
-      <c r="C3" s="283"/>
+      <c r="A3" s="280"/>
+      <c r="B3" s="282"/>
+      <c r="C3" s="284"/>
       <c r="D3" s="91"/>
       <c r="E3" s="92"/>
       <c r="F3" s="93" t="s">
@@ -34245,18 +34250,18 @@
       <c r="H3" s="90"/>
     </row>
     <row r="4" spans="1:8" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="287" t="s">
+      <c r="A4" s="288" t="s">
         <v>13</v>
       </c>
-      <c r="B4" s="286"/>
+      <c r="B4" s="287"/>
       <c r="C4" s="97" t="s">
         <v>87</v>
       </c>
-      <c r="D4" s="284" t="s">
+      <c r="D4" s="285" t="s">
         <v>14</v>
       </c>
-      <c r="E4" s="285"/>
-      <c r="F4" s="286"/>
+      <c r="E4" s="286"/>
+      <c r="F4" s="287"/>
       <c r="G4" s="95">
         <v>45795</v>
       </c>
@@ -34273,10 +34278,10 @@
       <c r="H5" s="9"/>
     </row>
     <row r="6" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A6" s="272" t="s">
+      <c r="A6" s="273" t="s">
         <v>15</v>
       </c>
-      <c r="B6" s="273"/>
+      <c r="B6" s="274"/>
       <c r="C6" s="98" t="s">
         <v>143</v>
       </c>
@@ -34287,10 +34292,10 @@
       <c r="H6" s="101"/>
     </row>
     <row r="7" spans="1:8" ht="31.5" x14ac:dyDescent="0.25">
-      <c r="A7" s="274"/>
-      <c r="B7" s="275"/>
+      <c r="A7" s="275"/>
+      <c r="B7" s="276"/>
       <c r="C7" s="102" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="D7" s="103"/>
       <c r="E7" s="104"/>
@@ -34299,10 +34304,10 @@
       <c r="H7" s="105"/>
     </row>
     <row r="8" spans="1:8" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="276"/>
-      <c r="B8" s="277"/>
+      <c r="A8" s="277"/>
+      <c r="B8" s="278"/>
       <c r="C8" s="106" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="D8" s="107"/>
       <c r="E8" s="108"/>
@@ -34473,7 +34478,7 @@
         <v>146</v>
       </c>
       <c r="C17" s="122" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="D17" s="234" t="s">
         <v>149</v>
@@ -34481,7 +34486,7 @@
       <c r="E17" s="233"/>
       <c r="F17" s="125"/>
       <c r="G17" s="122" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="H17" s="125"/>
     </row>
@@ -34514,7 +34519,7 @@
         <v>146</v>
       </c>
       <c r="C19" s="125" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="D19" s="234" t="s">
         <v>149</v>
@@ -34522,7 +34527,7 @@
       <c r="E19" s="233"/>
       <c r="F19" s="125"/>
       <c r="G19" s="125" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="H19" s="125"/>
     </row>
@@ -34531,7 +34536,7 @@
         <v>8</v>
       </c>
       <c r="B20" s="126" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C20" s="122" t="s">
         <v>29</v>
@@ -34555,7 +34560,7 @@
         <v>146</v>
       </c>
       <c r="C21" s="125" t="s">
-        <v>152</v>
+        <v>185</v>
       </c>
       <c r="D21" s="234"/>
       <c r="E21" s="234" t="s">
@@ -34563,7 +34568,7 @@
       </c>
       <c r="F21" s="125"/>
       <c r="G21" s="127" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="H21" s="125">
         <v>1</v>
@@ -34574,7 +34579,7 @@
         <v>10</v>
       </c>
       <c r="B22" s="126" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="C22" s="122" t="s">
         <v>29</v>
@@ -34598,7 +34603,7 @@
         <v>146</v>
       </c>
       <c r="C23" s="125" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="D23" s="234" t="s">
         <v>149</v>
@@ -34606,7 +34611,7 @@
       <c r="E23" s="234"/>
       <c r="F23" s="125"/>
       <c r="G23" s="125" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="H23" s="125"/>
     </row>
@@ -34615,7 +34620,7 @@
         <v>12</v>
       </c>
       <c r="B24" s="126" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="C24" s="122" t="s">
         <v>29</v>
@@ -34636,10 +34641,10 @@
         <v>13</v>
       </c>
       <c r="B25" s="122" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="C25" s="127" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="D25" s="234" t="s">
         <v>27</v>
@@ -34647,7 +34652,7 @@
       <c r="E25" s="234"/>
       <c r="F25" s="125"/>
       <c r="G25" s="127" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="H25" s="125"/>
     </row>
@@ -34656,7 +34661,7 @@
         <v>14</v>
       </c>
       <c r="B26" s="126" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="C26" s="122" t="s">
         <v>29</v>
@@ -34676,10 +34681,10 @@
         <v>15</v>
       </c>
       <c r="B27" s="122" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="C27" s="125" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D27" s="234" t="s">
         <v>149</v>
@@ -34687,7 +34692,7 @@
       <c r="E27" s="234"/>
       <c r="F27" s="125"/>
       <c r="G27" s="127" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="H27" s="125"/>
     </row>
@@ -34697,7 +34702,7 @@
         <v>16</v>
       </c>
       <c r="B28" s="126" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="C28" s="122" t="s">
         <v>29</v>
@@ -34717,10 +34722,10 @@
         <v>17</v>
       </c>
       <c r="B29" s="122" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="C29" s="125" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="D29" s="234" t="s">
         <v>149</v>
@@ -34728,7 +34733,7 @@
       <c r="E29" s="234"/>
       <c r="F29" s="125"/>
       <c r="G29" s="127" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="H29" s="125"/>
     </row>
@@ -35738,66 +35743,66 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="288" t="s">
+      <c r="A1" s="295" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="289"/>
+      <c r="B1" s="296"/>
       <c r="C1" s="129" t="s">
         <v>114</v>
       </c>
-      <c r="D1" s="289" t="s">
+      <c r="D1" s="296" t="s">
         <v>9</v>
       </c>
-      <c r="E1" s="289"/>
-      <c r="F1" s="289"/>
+      <c r="E1" s="296"/>
+      <c r="F1" s="296"/>
       <c r="G1" s="135" t="s">
         <v>36</v>
       </c>
       <c r="H1" s="138"/>
     </row>
     <row r="2" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A2" s="292" t="s">
+      <c r="A2" s="299" t="s">
         <v>10</v>
       </c>
-      <c r="B2" s="293"/>
-      <c r="C2" s="295" t="s">
-        <v>168</v>
-      </c>
-      <c r="D2" s="294" t="s">
+      <c r="B2" s="300"/>
+      <c r="C2" s="302" t="s">
+        <v>166</v>
+      </c>
+      <c r="D2" s="301" t="s">
         <v>11</v>
       </c>
-      <c r="E2" s="294"/>
-      <c r="F2" s="294"/>
+      <c r="E2" s="301"/>
+      <c r="F2" s="301"/>
       <c r="G2" s="136" t="s">
         <v>35</v>
       </c>
       <c r="H2" s="139"/>
     </row>
     <row r="3" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A3" s="292"/>
-      <c r="B3" s="293"/>
-      <c r="C3" s="296"/>
-      <c r="D3" s="294" t="s">
+      <c r="A3" s="299"/>
+      <c r="B3" s="300"/>
+      <c r="C3" s="303"/>
+      <c r="D3" s="301" t="s">
         <v>12</v>
       </c>
-      <c r="E3" s="294"/>
-      <c r="F3" s="294"/>
+      <c r="E3" s="301"/>
+      <c r="F3" s="301"/>
       <c r="G3" s="137"/>
       <c r="H3" s="139"/>
     </row>
     <row r="4" spans="1:8" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="290" t="s">
+      <c r="A4" s="297" t="s">
         <v>13</v>
       </c>
-      <c r="B4" s="291"/>
+      <c r="B4" s="298"/>
       <c r="C4" s="133" t="s">
         <v>86</v>
       </c>
-      <c r="D4" s="291" t="s">
+      <c r="D4" s="298" t="s">
         <v>14</v>
       </c>
-      <c r="E4" s="291"/>
-      <c r="F4" s="291"/>
+      <c r="E4" s="298"/>
+      <c r="F4" s="298"/>
       <c r="G4" s="169">
         <v>45795</v>
       </c>
@@ -35814,10 +35819,10 @@
       <c r="H5" s="17"/>
     </row>
     <row r="6" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A6" s="297" t="s">
+      <c r="A6" s="289" t="s">
         <v>15</v>
       </c>
-      <c r="B6" s="298"/>
+      <c r="B6" s="290"/>
       <c r="C6" s="98" t="s">
         <v>143</v>
       </c>
@@ -35828,10 +35833,10 @@
       <c r="H6" s="143"/>
     </row>
     <row r="7" spans="1:8" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="299"/>
-      <c r="B7" s="300"/>
+      <c r="A7" s="291"/>
+      <c r="B7" s="292"/>
       <c r="C7" s="150" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="D7" s="144"/>
       <c r="E7" s="145"/>
@@ -35840,10 +35845,10 @@
       <c r="H7" s="146"/>
     </row>
     <row r="8" spans="1:8" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="301"/>
-      <c r="B8" s="302"/>
+      <c r="A8" s="293"/>
+      <c r="B8" s="294"/>
       <c r="C8" s="151" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="D8" s="147"/>
       <c r="E8" s="148"/>
@@ -35928,10 +35933,10 @@
         <v>1</v>
       </c>
       <c r="B13" s="153" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="C13" s="154" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="D13" s="155" t="s">
         <v>27</v>
@@ -35939,7 +35944,7 @@
       <c r="E13" s="156"/>
       <c r="F13" s="156"/>
       <c r="G13" s="154" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="H13" s="157"/>
     </row>
@@ -35948,10 +35953,10 @@
         <v>2</v>
       </c>
       <c r="B14" s="153" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="C14" s="154" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="D14" s="155" t="s">
         <v>149</v>
@@ -35959,7 +35964,7 @@
       <c r="E14" s="159"/>
       <c r="F14" s="159"/>
       <c r="G14" s="154" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="H14" s="160"/>
     </row>
@@ -35968,10 +35973,10 @@
         <v>3</v>
       </c>
       <c r="B15" s="153" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="C15" s="154" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="D15" s="161" t="s">
         <v>27</v>
@@ -35979,7 +35984,7 @@
       <c r="E15" s="162"/>
       <c r="F15" s="162"/>
       <c r="G15" s="154" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="H15" s="163"/>
     </row>
@@ -35988,10 +35993,10 @@
         <v>4</v>
       </c>
       <c r="B16" s="153" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="C16" s="165" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="D16" s="166" t="s">
         <v>149</v>
@@ -35999,7 +36004,7 @@
       <c r="E16" s="167"/>
       <c r="F16" s="167"/>
       <c r="G16" s="165" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="H16" s="167"/>
     </row>
@@ -36008,10 +36013,10 @@
         <v>5</v>
       </c>
       <c r="B17" s="153" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="C17" s="154" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="D17" s="168" t="s">
         <v>27</v>
@@ -36019,7 +36024,7 @@
       <c r="E17" s="167"/>
       <c r="F17" s="167"/>
       <c r="G17" s="154" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="H17" s="167"/>
     </row>
@@ -36028,10 +36033,10 @@
         <v>6</v>
       </c>
       <c r="B18" s="153" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="C18" s="165" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="D18" s="166" t="s">
         <v>149</v>
@@ -36039,7 +36044,7 @@
       <c r="E18" s="167"/>
       <c r="F18" s="167"/>
       <c r="G18" s="165" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="H18" s="167"/>
     </row>
@@ -36048,10 +36053,10 @@
         <v>7</v>
       </c>
       <c r="B19" s="153" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="C19" s="154" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="D19" s="166" t="s">
         <v>27</v>
@@ -36059,7 +36064,7 @@
       <c r="E19" s="167"/>
       <c r="F19" s="167"/>
       <c r="G19" s="154" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="H19" s="167"/>
     </row>
@@ -36068,10 +36073,10 @@
         <v>8</v>
       </c>
       <c r="B20" s="153" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="C20" s="165" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="D20" s="166" t="s">
         <v>27</v>
@@ -36079,7 +36084,7 @@
       <c r="E20" s="167"/>
       <c r="F20" s="167"/>
       <c r="G20" s="165" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="H20" s="167"/>
     </row>
@@ -36111,68 +36116,68 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="32.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="297" t="s">
+      <c r="A1" s="289" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="298"/>
+      <c r="B1" s="290"/>
       <c r="C1" s="171" t="s">
         <v>69</v>
       </c>
-      <c r="D1" s="312" t="s">
+      <c r="D1" s="313" t="s">
         <v>9</v>
       </c>
-      <c r="E1" s="313"/>
-      <c r="F1" s="314"/>
+      <c r="E1" s="314"/>
+      <c r="F1" s="315"/>
       <c r="G1" s="130" t="s">
         <v>38</v>
       </c>
       <c r="H1" s="131"/>
     </row>
     <row r="2" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A2" s="299" t="s">
+      <c r="A2" s="291" t="s">
         <v>10</v>
       </c>
-      <c r="B2" s="300"/>
-      <c r="C2" s="310" t="s">
-        <v>180</v>
-      </c>
-      <c r="D2" s="315" t="s">
+      <c r="B2" s="292"/>
+      <c r="C2" s="311" t="s">
+        <v>178</v>
+      </c>
+      <c r="D2" s="316" t="s">
         <v>11</v>
       </c>
-      <c r="E2" s="316"/>
-      <c r="F2" s="317"/>
+      <c r="E2" s="317"/>
+      <c r="F2" s="318"/>
       <c r="G2" s="128" t="s">
         <v>35</v>
       </c>
       <c r="H2" s="132"/>
     </row>
     <row r="3" spans="1:8" ht="48" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="299"/>
-      <c r="B3" s="300"/>
-      <c r="C3" s="311"/>
-      <c r="D3" s="318" t="s">
+      <c r="A3" s="291"/>
+      <c r="B3" s="292"/>
+      <c r="C3" s="312"/>
+      <c r="D3" s="319" t="s">
         <v>12</v>
       </c>
-      <c r="E3" s="319"/>
-      <c r="F3" s="320"/>
+      <c r="E3" s="320"/>
+      <c r="F3" s="321"/>
       <c r="G3" s="186">
         <v>2</v>
       </c>
       <c r="H3" s="132"/>
     </row>
     <row r="4" spans="1:8" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="290" t="s">
+      <c r="A4" s="297" t="s">
         <v>13</v>
       </c>
-      <c r="B4" s="291"/>
+      <c r="B4" s="298"/>
       <c r="C4" s="172" t="s">
         <v>88</v>
       </c>
-      <c r="D4" s="303" t="s">
+      <c r="D4" s="304" t="s">
         <v>14</v>
       </c>
-      <c r="E4" s="304"/>
-      <c r="F4" s="305"/>
+      <c r="E4" s="305"/>
+      <c r="F4" s="306"/>
       <c r="G4" s="170">
         <v>45795</v>
       </c>
@@ -36189,10 +36194,10 @@
       <c r="H5" s="17"/>
     </row>
     <row r="6" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A6" s="306" t="s">
+      <c r="A6" s="307" t="s">
         <v>15</v>
       </c>
-      <c r="B6" s="307"/>
+      <c r="B6" s="308"/>
       <c r="C6" s="98" t="s">
         <v>143</v>
       </c>
@@ -36203,10 +36208,10 @@
       <c r="H6" s="176"/>
     </row>
     <row r="7" spans="1:8" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="308"/>
-      <c r="B7" s="309"/>
+      <c r="A7" s="309"/>
+      <c r="B7" s="310"/>
       <c r="C7" s="177" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="D7" s="178"/>
       <c r="E7" s="179"/>
@@ -36301,10 +36306,10 @@
         <v>1</v>
       </c>
       <c r="B13" s="182" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="C13" s="182" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="D13" s="183" t="s">
         <v>33</v>
@@ -36312,7 +36317,7 @@
       <c r="E13" s="182"/>
       <c r="F13" s="184"/>
       <c r="G13" s="182" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="H13" s="182"/>
     </row>
@@ -36321,10 +36326,10 @@
         <v>2</v>
       </c>
       <c r="B14" s="182" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C14" s="182" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="D14" s="183" t="s">
         <v>33</v>
@@ -36332,7 +36337,7 @@
       <c r="E14" s="182"/>
       <c r="F14" s="184"/>
       <c r="G14" s="182" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="H14" s="182"/>
     </row>
@@ -36341,10 +36346,10 @@
         <v>3</v>
       </c>
       <c r="B15" s="182" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="C15" s="182" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="D15" s="183" t="s">
         <v>33</v>
@@ -36352,7 +36357,7 @@
       <c r="E15" s="182"/>
       <c r="F15" s="184"/>
       <c r="G15" s="182" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="H15" s="182"/>
     </row>
@@ -36361,10 +36366,10 @@
         <v>4</v>
       </c>
       <c r="B16" s="182" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="C16" s="182" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="D16" s="183" t="s">
         <v>33</v>
@@ -36372,7 +36377,7 @@
       <c r="E16" s="182"/>
       <c r="F16" s="184"/>
       <c r="G16" s="182" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="H16" s="182"/>
     </row>
@@ -36381,10 +36386,10 @@
         <v>5</v>
       </c>
       <c r="B17" s="182" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="C17" s="182" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="D17" s="183" t="s">
         <v>33</v>
@@ -36392,7 +36397,7 @@
       <c r="E17" s="182"/>
       <c r="F17" s="184"/>
       <c r="G17" s="182" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="H17" s="182"/>
     </row>
@@ -36401,18 +36406,18 @@
         <v>6</v>
       </c>
       <c r="B18" s="182" t="s">
+        <v>186</v>
+      </c>
+      <c r="C18" s="185" t="s">
         <v>188</v>
-      </c>
-      <c r="C18" s="185" t="s">
-        <v>190</v>
       </c>
       <c r="D18" s="167"/>
       <c r="E18" s="166" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="F18" s="167"/>
       <c r="G18" s="185" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="H18" s="164">
         <v>2</v>
@@ -36446,68 +36451,68 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="333" t="s">
+      <c r="A1" s="334" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="334"/>
+      <c r="B1" s="335"/>
       <c r="C1" s="187" t="s">
-        <v>191</v>
-      </c>
-      <c r="D1" s="329" t="s">
+        <v>189</v>
+      </c>
+      <c r="D1" s="330" t="s">
         <v>9</v>
       </c>
-      <c r="E1" s="329"/>
-      <c r="F1" s="329"/>
+      <c r="E1" s="330"/>
+      <c r="F1" s="330"/>
       <c r="G1" s="189" t="s">
         <v>39</v>
       </c>
       <c r="H1" s="192"/>
     </row>
     <row r="2" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A2" s="335" t="s">
+      <c r="A2" s="336" t="s">
         <v>10</v>
       </c>
-      <c r="B2" s="336"/>
-      <c r="C2" s="332" t="s">
-        <v>192</v>
-      </c>
-      <c r="D2" s="330" t="s">
+      <c r="B2" s="337"/>
+      <c r="C2" s="333" t="s">
+        <v>190</v>
+      </c>
+      <c r="D2" s="331" t="s">
         <v>11</v>
       </c>
-      <c r="E2" s="330"/>
-      <c r="F2" s="330"/>
+      <c r="E2" s="331"/>
+      <c r="F2" s="331"/>
       <c r="G2" s="190" t="s">
         <v>35</v>
       </c>
       <c r="H2" s="193"/>
     </row>
     <row r="3" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A3" s="335"/>
-      <c r="B3" s="336"/>
-      <c r="C3" s="332"/>
-      <c r="D3" s="330" t="s">
+      <c r="A3" s="336"/>
+      <c r="B3" s="337"/>
+      <c r="C3" s="333"/>
+      <c r="D3" s="331" t="s">
         <v>12</v>
       </c>
-      <c r="E3" s="330"/>
-      <c r="F3" s="330"/>
+      <c r="E3" s="331"/>
+      <c r="F3" s="331"/>
       <c r="G3" s="251">
         <v>3</v>
       </c>
       <c r="H3" s="193"/>
     </row>
     <row r="4" spans="1:8" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="327" t="s">
+      <c r="A4" s="328" t="s">
         <v>13</v>
       </c>
-      <c r="B4" s="328"/>
+      <c r="B4" s="329"/>
       <c r="C4" s="188" t="s">
         <v>85</v>
       </c>
-      <c r="D4" s="331" t="s">
+      <c r="D4" s="332" t="s">
         <v>14</v>
       </c>
-      <c r="E4" s="331"/>
-      <c r="F4" s="331"/>
+      <c r="E4" s="332"/>
+      <c r="F4" s="332"/>
       <c r="G4" s="191">
         <v>45795</v>
       </c>
@@ -36524,10 +36529,10 @@
       <c r="H5" s="23"/>
     </row>
     <row r="6" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A6" s="321" t="s">
+      <c r="A6" s="322" t="s">
         <v>15</v>
       </c>
-      <c r="B6" s="322"/>
+      <c r="B6" s="323"/>
       <c r="C6" s="98" t="s">
         <v>143</v>
       </c>
@@ -36538,10 +36543,10 @@
       <c r="H6" s="196"/>
     </row>
     <row r="7" spans="1:8" ht="17.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="323"/>
-      <c r="B7" s="324"/>
+      <c r="A7" s="324"/>
+      <c r="B7" s="325"/>
       <c r="C7" s="150" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="D7" s="173"/>
       <c r="E7" s="197"/>
@@ -36550,10 +36555,10 @@
       <c r="H7" s="198"/>
     </row>
     <row r="8" spans="1:8" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="325"/>
-      <c r="B8" s="326"/>
+      <c r="A8" s="326"/>
+      <c r="B8" s="327"/>
       <c r="C8" s="199" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="D8" s="200"/>
       <c r="E8" s="201"/>
@@ -36638,10 +36643,10 @@
         <v>1</v>
       </c>
       <c r="B13" s="213" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="C13" s="213" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="D13" s="223" t="s">
         <v>27</v>
@@ -36649,7 +36654,7 @@
       <c r="E13" s="223"/>
       <c r="F13" s="214"/>
       <c r="G13" s="213" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="H13" s="215"/>
     </row>
@@ -36658,10 +36663,10 @@
         <v>2</v>
       </c>
       <c r="B14" s="213" t="s">
+        <v>194</v>
+      </c>
+      <c r="C14" s="213" t="s">
         <v>196</v>
-      </c>
-      <c r="C14" s="213" t="s">
-        <v>198</v>
       </c>
       <c r="D14" s="223" t="s">
         <v>27</v>
@@ -36669,7 +36674,7 @@
       <c r="E14" s="224"/>
       <c r="F14" s="216"/>
       <c r="G14" s="213" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="H14" s="217"/>
     </row>
@@ -36678,10 +36683,10 @@
         <v>3</v>
       </c>
       <c r="B15" s="218" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="C15" s="218" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="D15" s="225"/>
       <c r="E15" s="226" t="s">
@@ -36689,7 +36694,7 @@
       </c>
       <c r="F15" s="219"/>
       <c r="G15" s="218" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="H15" s="220">
         <v>3</v>
@@ -36700,10 +36705,10 @@
         <v>4</v>
       </c>
       <c r="B16" s="221" t="s">
+        <v>200</v>
+      </c>
+      <c r="C16" s="221" t="s">
         <v>202</v>
-      </c>
-      <c r="C16" s="221" t="s">
-        <v>204</v>
       </c>
       <c r="D16" s="227" t="s">
         <v>27</v>
@@ -36711,7 +36716,7 @@
       <c r="E16" s="227"/>
       <c r="F16" s="222"/>
       <c r="G16" s="221" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="H16" s="222"/>
     </row>
